--- a/ParaBank_Final_Master_QA_Documentation.xlsx
+++ b/ParaBank_Final_Master_QA_Documentation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\muska\Documents\CAPSTONE\CAPSTONE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8504276-A4BF-459B-A861-74BE9E04A6FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAD81053-7C9A-4867-AA89-5F0294477341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="867" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="867" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Plan" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="447">
   <si>
     <t>Defect ID</t>
   </si>
@@ -67,9 +67,6 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Evidence</t>
-  </si>
-  <si>
     <t>BUG-001</t>
   </si>
   <si>
@@ -79,20 +76,10 @@
     <t>FR-09</t>
   </si>
   <si>
-    <t>GET /accounts/{accountId} does not return expected 404 status code for non-existent account ID</t>
-  </si>
-  <si>
-    <t>1. Send GET /accounts/999999 via REST API Client.
-2. Verify the HTTP status code of the response.</t>
-  </si>
-  <si>
     <t>Medium</t>
   </si>
   <si>
     <t>Open</t>
-  </si>
-  <si>
-    <t>evidence/api_response_non_existent.json</t>
   </si>
   <si>
     <t>BUG-002</t>
@@ -113,16 +100,10 @@
     <t>High</t>
   </si>
   <si>
-    <t>evidence/screenshot_overdraft_transfer_allowed.png</t>
-  </si>
-  <si>
     <t>BUG-003</t>
   </si>
   <si>
     <t>TC-TX-UI-03</t>
-  </si>
-  <si>
-    <t>evidence/screenshot_empty_transfer_warning.png</t>
   </si>
   <si>
     <t>BUG-004</t>
@@ -138,9 +119,6 @@
 2. Observe response code and balance changes.</t>
   </si>
   <si>
-    <t>evidence/api_response_insufficient_funds.json</t>
-  </si>
-  <si>
     <t>BUG-005</t>
   </si>
   <si>
@@ -148,9 +126,6 @@
   </si>
   <si>
     <t>TC-TX-UI-04</t>
-  </si>
-  <si>
-    <t>evidence/screenshot_alpha_transfer_warning.png</t>
   </si>
   <si>
     <t>PARABANK CAPSTONE – CONSOLIDATED TEST PLAN</t>
@@ -1110,33 +1085,6 @@
   </si>
   <si>
     <t>—</t>
-  </si>
-  <si>
-    <t>evidence/api_response_customer_accounts.json</t>
-  </si>
-  <si>
-    <t>evidence/api_response_account_details.json</t>
-  </si>
-  <si>
-    <t>evidence/api_response_create_account.json</t>
-  </si>
-  <si>
-    <t>evidence/api_response_post_transfer.json</t>
-  </si>
-  <si>
-    <t>evidence/api_response_source_debit.json</t>
-  </si>
-  <si>
-    <t>evidence/api_response_dest_credit.json</t>
-  </si>
-  <si>
-    <t>evidence/api_response_source_transactions.json</t>
-  </si>
-  <si>
-    <t>evidence/screenshot_e2e_provisioning.png</t>
-  </si>
-  <si>
-    <t>evidence/screenshot_e2e_transfer.png</t>
   </si>
   <si>
     <t>Title / Area</t>
@@ -1468,36 +1416,6 @@
     <t>The manual and automated test suites have completed execution. Out of 22 designed test cases, 18 passed, and 5 negative test cases (TC-TX-UI-03, TC-TX-UI-04, TC-TX-UI-05, TC-API-08, TC-API-09) failed due to application validation and error handling bugs (allowing negative/blank/alphabetic amounts, overdrafts, and invalid status codes). The core functional flows for account creation, retrieval, and fund transfers are stable. It is recommended to deploy the build with hotfixes for the logged defects (BUG-001, BUG-002, BUG-003, BUG-004, BUG-005) to ensure robust validation in production.</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1NDgXn3mQ6qaFI7ZiXY6rJ_yFhOJiCrgT/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1g6IXhzXImPDhScpGAHFjL_cHlchQaKtW/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1VRmUv51dWZ3kJZh4RT6smxHzSjRXM6Mg/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/15PHwfT5OZ1f68LlmAZvJ80QOM4XcEB0N/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/10Ck-D4zX8hhR7OB_BXJRfTIPb0iHWJSq/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1iCg4u0Tj1pDM-CcmoPP1wsbrqnEjE-C3/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/152oCcdRjkWafJQnu4IpYh6rtxF4_A-yJ/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1-FZBr7knFfpL0uhtDQm_o35IK7wgce0l/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1kljI_mpE4lBJMmCZZLEiVI70NaipzJ0g/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1OCyygmi6lmIMdeIK86alx_Fw98gAahlo/view?usp=drive_link</t>
-  </si>
-  <si>
     <t>Registring new user</t>
   </si>
   <si>
@@ -1564,9 +1482,6 @@
     <t>BUG-006</t>
   </si>
   <si>
-    <t>Covered (5  defect: BUG-001, BUG-002, BUG-003, BUG-004, BUG-005, BUG-006)</t>
-  </si>
-  <si>
     <t>Verify transfer fails when negative amount is entered.</t>
   </si>
   <si>
@@ -1599,13 +1514,16 @@
   </si>
   <si>
     <t>10 executed – 10 Passed</t>
+  </si>
+  <si>
+    <t>Covered (5  defect: BUG-001, BUG-002, BUG-003, BUG-004, BUG-005)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1616,20 +1534,6 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
@@ -1715,11 +1619,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1735,9 +1638,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1749,30 +1649,22 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1780,9 +1672,13 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2084,17 +1980,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V60"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="85" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="22"/>
+        <v>28</v>
+      </c>
+      <c r="B1" s="24"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -2116,7 +2012,7 @@
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2140,12 +2036,12 @@
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
     </row>
-    <row r="3" spans="1:22" ht="43.2" customHeight="1">
-      <c r="A3" s="8" t="s">
-        <v>37</v>
+    <row r="3" spans="1:22" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -2168,12 +2064,12 @@
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
     </row>
-    <row r="4" spans="1:22" ht="100.8" customHeight="1">
-      <c r="A4" s="8" t="s">
-        <v>39</v>
+    <row r="4" spans="1:22" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -2196,12 +2092,12 @@
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
     </row>
-    <row r="5" spans="1:22" ht="172.8" customHeight="1">
-      <c r="A5" s="8" t="s">
-        <v>41</v>
+    <row r="5" spans="1:22" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -2224,12 +2120,12 @@
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
     </row>
-    <row r="6" spans="1:22" ht="72" customHeight="1">
-      <c r="A6" s="8" t="s">
-        <v>43</v>
+    <row r="6" spans="1:22" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -2252,12 +2148,12 @@
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
     </row>
-    <row r="7" spans="1:22" ht="72" customHeight="1">
-      <c r="A7" s="8" t="s">
-        <v>45</v>
+    <row r="7" spans="1:22" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>37</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -2280,12 +2176,12 @@
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
     </row>
-    <row r="8" spans="1:22" ht="57.6" customHeight="1">
-      <c r="A8" s="8" t="s">
-        <v>47</v>
+    <row r="8" spans="1:22" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>39</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -2308,12 +2204,12 @@
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
     </row>
-    <row r="9" spans="1:22" ht="57.6" customHeight="1">
-      <c r="A9" s="8" t="s">
-        <v>49</v>
+    <row r="9" spans="1:22" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>41</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -2336,12 +2232,12 @@
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
     </row>
-    <row r="10" spans="1:22" ht="57.6" customHeight="1">
-      <c r="A10" s="8" t="s">
-        <v>51</v>
+    <row r="10" spans="1:22" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -2364,12 +2260,12 @@
       <c r="U10" s="1"/>
       <c r="V10" s="1"/>
     </row>
-    <row r="11" spans="1:22" ht="57.6" customHeight="1">
-      <c r="A11" s="8" t="s">
-        <v>53</v>
+    <row r="11" spans="1:22" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>45</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -2392,12 +2288,12 @@
       <c r="U11" s="1"/>
       <c r="V11" s="1"/>
     </row>
-    <row r="12" spans="1:22" ht="57.6" customHeight="1">
-      <c r="A12" s="8" t="s">
-        <v>55</v>
+    <row r="12" spans="1:22" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -2420,12 +2316,12 @@
       <c r="U12" s="1"/>
       <c r="V12" s="1"/>
     </row>
-    <row r="13" spans="1:22" ht="72" customHeight="1">
-      <c r="A13" s="8" t="s">
-        <v>57</v>
+    <row r="13" spans="1:22" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>49</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -2448,12 +2344,12 @@
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
     </row>
-    <row r="14" spans="1:22" ht="144">
-      <c r="A14" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>421</v>
+    <row r="14" spans="1:22" ht="144" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>404</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -2476,7 +2372,7 @@
       <c r="U14" s="1"/>
       <c r="V14" s="1"/>
     </row>
-    <row r="15" spans="1:22">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -2500,7 +2396,7 @@
       <c r="U15" s="1"/>
       <c r="V15" s="1"/>
     </row>
-    <row r="16" spans="1:22">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -2524,7 +2420,7 @@
       <c r="U16" s="1"/>
       <c r="V16" s="1"/>
     </row>
-    <row r="17" spans="1:22">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -2548,7 +2444,7 @@
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
     </row>
-    <row r="18" spans="1:22">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -2572,7 +2468,7 @@
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
     </row>
-    <row r="19" spans="1:22">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -2596,7 +2492,7 @@
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
     </row>
-    <row r="20" spans="1:22">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -2620,7 +2516,7 @@
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
     </row>
-    <row r="21" spans="1:22">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -2644,7 +2540,7 @@
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
     </row>
-    <row r="22" spans="1:22">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -2668,7 +2564,7 @@
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
     </row>
-    <row r="23" spans="1:22">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -2692,7 +2588,7 @@
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
     </row>
-    <row r="24" spans="1:22">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -2716,7 +2612,7 @@
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
     </row>
-    <row r="25" spans="1:22">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -2740,7 +2636,7 @@
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
     </row>
-    <row r="26" spans="1:22">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -2764,7 +2660,7 @@
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
     </row>
-    <row r="27" spans="1:22">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -2788,7 +2684,7 @@
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
     </row>
-    <row r="28" spans="1:22">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -2812,7 +2708,7 @@
       <c r="U28" s="1"/>
       <c r="V28" s="1"/>
     </row>
-    <row r="29" spans="1:22">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -2836,7 +2732,7 @@
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
     </row>
-    <row r="30" spans="1:22">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -2860,7 +2756,7 @@
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
     </row>
-    <row r="31" spans="1:22">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -2884,7 +2780,7 @@
       <c r="U31" s="1"/>
       <c r="V31" s="1"/>
     </row>
-    <row r="32" spans="1:22">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -2908,7 +2804,7 @@
       <c r="U32" s="1"/>
       <c r="V32" s="1"/>
     </row>
-    <row r="33" spans="1:22">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -2932,7 +2828,7 @@
       <c r="U33" s="1"/>
       <c r="V33" s="1"/>
     </row>
-    <row r="34" spans="1:22">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -2956,7 +2852,7 @@
       <c r="U34" s="1"/>
       <c r="V34" s="1"/>
     </row>
-    <row r="35" spans="1:22">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -2980,7 +2876,7 @@
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
     </row>
-    <row r="36" spans="1:22">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -3004,7 +2900,7 @@
       <c r="U36" s="1"/>
       <c r="V36" s="1"/>
     </row>
-    <row r="37" spans="1:22">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -3028,7 +2924,7 @@
       <c r="U37" s="1"/>
       <c r="V37" s="1"/>
     </row>
-    <row r="38" spans="1:22">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -3052,7 +2948,7 @@
       <c r="U38" s="1"/>
       <c r="V38" s="1"/>
     </row>
-    <row r="39" spans="1:22">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -3076,7 +2972,7 @@
       <c r="U39" s="1"/>
       <c r="V39" s="1"/>
     </row>
-    <row r="40" spans="1:22">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -3100,7 +2996,7 @@
       <c r="U40" s="1"/>
       <c r="V40" s="1"/>
     </row>
-    <row r="41" spans="1:22">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -3124,7 +3020,7 @@
       <c r="U41" s="1"/>
       <c r="V41" s="1"/>
     </row>
-    <row r="42" spans="1:22">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -3148,7 +3044,7 @@
       <c r="U42" s="1"/>
       <c r="V42" s="1"/>
     </row>
-    <row r="43" spans="1:22">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -3172,7 +3068,7 @@
       <c r="U43" s="1"/>
       <c r="V43" s="1"/>
     </row>
-    <row r="44" spans="1:22">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -3196,7 +3092,7 @@
       <c r="U44" s="1"/>
       <c r="V44" s="1"/>
     </row>
-    <row r="45" spans="1:22">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -3220,7 +3116,7 @@
       <c r="U45" s="1"/>
       <c r="V45" s="1"/>
     </row>
-    <row r="46" spans="1:22">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -3244,7 +3140,7 @@
       <c r="U46" s="1"/>
       <c r="V46" s="1"/>
     </row>
-    <row r="47" spans="1:22">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -3268,7 +3164,7 @@
       <c r="U47" s="1"/>
       <c r="V47" s="1"/>
     </row>
-    <row r="48" spans="1:22">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -3292,7 +3188,7 @@
       <c r="U48" s="1"/>
       <c r="V48" s="1"/>
     </row>
-    <row r="49" spans="1:22">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -3316,7 +3212,7 @@
       <c r="U49" s="1"/>
       <c r="V49" s="1"/>
     </row>
-    <row r="50" spans="1:22">
+    <row r="50" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -3340,7 +3236,7 @@
       <c r="U50" s="1"/>
       <c r="V50" s="1"/>
     </row>
-    <row r="51" spans="1:22">
+    <row r="51" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -3364,7 +3260,7 @@
       <c r="U51" s="1"/>
       <c r="V51" s="1"/>
     </row>
-    <row r="52" spans="1:22">
+    <row r="52" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -3388,7 +3284,7 @@
       <c r="U52" s="1"/>
       <c r="V52" s="1"/>
     </row>
-    <row r="53" spans="1:22">
+    <row r="53" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -3412,7 +3308,7 @@
       <c r="U53" s="1"/>
       <c r="V53" s="1"/>
     </row>
-    <row r="54" spans="1:22">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -3436,7 +3332,7 @@
       <c r="U54" s="1"/>
       <c r="V54" s="1"/>
     </row>
-    <row r="55" spans="1:22">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -3460,7 +3356,7 @@
       <c r="U55" s="1"/>
       <c r="V55" s="1"/>
     </row>
-    <row r="56" spans="1:22">
+    <row r="56" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -3484,7 +3380,7 @@
       <c r="U56" s="1"/>
       <c r="V56" s="1"/>
     </row>
-    <row r="57" spans="1:22">
+    <row r="57" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -3508,7 +3404,7 @@
       <c r="U57" s="1"/>
       <c r="V57" s="1"/>
     </row>
-    <row r="58" spans="1:22">
+    <row r="58" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -3532,7 +3428,7 @@
       <c r="U58" s="1"/>
       <c r="V58" s="1"/>
     </row>
-    <row r="59" spans="1:22">
+    <row r="59" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -3556,7 +3452,7 @@
       <c r="U59" s="1"/>
       <c r="V59" s="1"/>
     </row>
-    <row r="60" spans="1:22">
+    <row r="60" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -3591,7 +3487,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:V60"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -3602,29 +3498,29 @@
     <col min="8" max="8" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
-      <c r="A1" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="G1" s="9" t="s">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="8" t="s">
         <v>8</v>
       </c>
       <c r="I1" s="1"/>
@@ -3642,30 +3538,30 @@
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
     </row>
-    <row r="2" spans="1:22" ht="28.8" customHeight="1">
+    <row r="2" spans="1:22" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -3682,30 +3578,30 @@
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
     </row>
-    <row r="3" spans="1:22" ht="28.8" customHeight="1">
+    <row r="3" spans="1:22" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
@@ -3722,30 +3618,30 @@
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
     </row>
-    <row r="4" spans="1:22" ht="28.8" customHeight="1">
+    <row r="4" spans="1:22" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="E4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>15</v>
-      </c>
       <c r="H4" s="5" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -3762,30 +3658,30 @@
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
     </row>
-    <row r="5" spans="1:22" ht="28.8" customHeight="1">
+    <row r="5" spans="1:22" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
@@ -3802,30 +3698,30 @@
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
     </row>
-    <row r="6" spans="1:22" ht="28.8" customHeight="1">
+    <row r="6" spans="1:22" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
@@ -3842,30 +3738,30 @@
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
@@ -3882,30 +3778,30 @@
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
     </row>
-    <row r="8" spans="1:22" ht="28.8" customHeight="1">
+    <row r="8" spans="1:22" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
@@ -3922,30 +3818,30 @@
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
     </row>
-    <row r="9" spans="1:22" ht="28.8">
+    <row r="9" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="B9" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>106</v>
-      </c>
       <c r="E9" s="5" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
@@ -3962,30 +3858,30 @@
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
     </row>
-    <row r="10" spans="1:22">
-      <c r="A10" s="12" t="s">
-        <v>413</v>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A10" s="11" t="s">
+        <v>396</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>414</v>
+        <v>397</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>416</v>
+        <v>399</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>422</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="G10" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>72</v>
+        <v>398</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>405</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="G10" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>64</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
@@ -4002,7 +3898,7 @@
       <c r="U10" s="1"/>
       <c r="V10" s="1"/>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -4026,7 +3922,7 @@
       <c r="U11" s="1"/>
       <c r="V11" s="1"/>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -4050,7 +3946,7 @@
       <c r="U12" s="1"/>
       <c r="V12" s="1"/>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -4074,7 +3970,7 @@
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -4098,7 +3994,7 @@
       <c r="U14" s="1"/>
       <c r="V14" s="1"/>
     </row>
-    <row r="15" spans="1:22">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -4122,7 +4018,7 @@
       <c r="U15" s="1"/>
       <c r="V15" s="1"/>
     </row>
-    <row r="16" spans="1:22">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -4146,7 +4042,7 @@
       <c r="U16" s="1"/>
       <c r="V16" s="1"/>
     </row>
-    <row r="17" spans="1:22">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -4170,7 +4066,7 @@
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
     </row>
-    <row r="18" spans="1:22">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -4194,7 +4090,7 @@
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
     </row>
-    <row r="19" spans="1:22">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -4218,7 +4114,7 @@
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
     </row>
-    <row r="20" spans="1:22">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -4242,7 +4138,7 @@
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
     </row>
-    <row r="21" spans="1:22">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -4266,7 +4162,7 @@
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
     </row>
-    <row r="22" spans="1:22">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -4290,7 +4186,7 @@
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
     </row>
-    <row r="23" spans="1:22">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -4314,7 +4210,7 @@
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
     </row>
-    <row r="24" spans="1:22">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -4338,7 +4234,7 @@
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
     </row>
-    <row r="25" spans="1:22">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -4362,7 +4258,7 @@
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
     </row>
-    <row r="26" spans="1:22">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -4386,7 +4282,7 @@
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
     </row>
-    <row r="27" spans="1:22">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -4410,7 +4306,7 @@
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
     </row>
-    <row r="28" spans="1:22">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -4434,7 +4330,7 @@
       <c r="U28" s="1"/>
       <c r="V28" s="1"/>
     </row>
-    <row r="29" spans="1:22">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -4458,7 +4354,7 @@
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
     </row>
-    <row r="30" spans="1:22">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -4482,7 +4378,7 @@
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
     </row>
-    <row r="31" spans="1:22">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -4506,7 +4402,7 @@
       <c r="U31" s="1"/>
       <c r="V31" s="1"/>
     </row>
-    <row r="32" spans="1:22">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -4530,7 +4426,7 @@
       <c r="U32" s="1"/>
       <c r="V32" s="1"/>
     </row>
-    <row r="33" spans="1:22">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -4554,7 +4450,7 @@
       <c r="U33" s="1"/>
       <c r="V33" s="1"/>
     </row>
-    <row r="34" spans="1:22">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -4578,7 +4474,7 @@
       <c r="U34" s="1"/>
       <c r="V34" s="1"/>
     </row>
-    <row r="35" spans="1:22">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -4602,7 +4498,7 @@
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
     </row>
-    <row r="36" spans="1:22">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -4626,7 +4522,7 @@
       <c r="U36" s="1"/>
       <c r="V36" s="1"/>
     </row>
-    <row r="37" spans="1:22">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -4650,7 +4546,7 @@
       <c r="U37" s="1"/>
       <c r="V37" s="1"/>
     </row>
-    <row r="38" spans="1:22">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -4674,7 +4570,7 @@
       <c r="U38" s="1"/>
       <c r="V38" s="1"/>
     </row>
-    <row r="39" spans="1:22">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -4698,7 +4594,7 @@
       <c r="U39" s="1"/>
       <c r="V39" s="1"/>
     </row>
-    <row r="40" spans="1:22">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -4722,7 +4618,7 @@
       <c r="U40" s="1"/>
       <c r="V40" s="1"/>
     </row>
-    <row r="41" spans="1:22">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -4746,7 +4642,7 @@
       <c r="U41" s="1"/>
       <c r="V41" s="1"/>
     </row>
-    <row r="42" spans="1:22">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -4770,7 +4666,7 @@
       <c r="U42" s="1"/>
       <c r="V42" s="1"/>
     </row>
-    <row r="43" spans="1:22">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -4794,7 +4690,7 @@
       <c r="U43" s="1"/>
       <c r="V43" s="1"/>
     </row>
-    <row r="44" spans="1:22">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -4818,7 +4714,7 @@
       <c r="U44" s="1"/>
       <c r="V44" s="1"/>
     </row>
-    <row r="45" spans="1:22">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -4842,7 +4738,7 @@
       <c r="U45" s="1"/>
       <c r="V45" s="1"/>
     </row>
-    <row r="46" spans="1:22">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -4866,7 +4762,7 @@
       <c r="U46" s="1"/>
       <c r="V46" s="1"/>
     </row>
-    <row r="47" spans="1:22">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -4890,7 +4786,7 @@
       <c r="U47" s="1"/>
       <c r="V47" s="1"/>
     </row>
-    <row r="48" spans="1:22">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -4914,7 +4810,7 @@
       <c r="U48" s="1"/>
       <c r="V48" s="1"/>
     </row>
-    <row r="49" spans="1:22">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -4938,7 +4834,7 @@
       <c r="U49" s="1"/>
       <c r="V49" s="1"/>
     </row>
-    <row r="50" spans="1:22">
+    <row r="50" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -4962,7 +4858,7 @@
       <c r="U50" s="1"/>
       <c r="V50" s="1"/>
     </row>
-    <row r="51" spans="1:22">
+    <row r="51" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -4986,7 +4882,7 @@
       <c r="U51" s="1"/>
       <c r="V51" s="1"/>
     </row>
-    <row r="52" spans="1:22">
+    <row r="52" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -5010,7 +4906,7 @@
       <c r="U52" s="1"/>
       <c r="V52" s="1"/>
     </row>
-    <row r="53" spans="1:22">
+    <row r="53" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -5034,7 +4930,7 @@
       <c r="U53" s="1"/>
       <c r="V53" s="1"/>
     </row>
-    <row r="54" spans="1:22">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -5058,7 +4954,7 @@
       <c r="U54" s="1"/>
       <c r="V54" s="1"/>
     </row>
-    <row r="55" spans="1:22">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -5082,7 +4978,7 @@
       <c r="U55" s="1"/>
       <c r="V55" s="1"/>
     </row>
-    <row r="56" spans="1:22">
+    <row r="56" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -5106,7 +5002,7 @@
       <c r="U56" s="1"/>
       <c r="V56" s="1"/>
     </row>
-    <row r="57" spans="1:22">
+    <row r="57" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -5130,7 +5026,7 @@
       <c r="U57" s="1"/>
       <c r="V57" s="1"/>
     </row>
-    <row r="58" spans="1:22">
+    <row r="58" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -5154,7 +5050,7 @@
       <c r="U58" s="1"/>
       <c r="V58" s="1"/>
     </row>
-    <row r="59" spans="1:22">
+    <row r="59" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -5178,7 +5074,7 @@
       <c r="U59" s="1"/>
       <c r="V59" s="1"/>
     </row>
-    <row r="60" spans="1:22">
+    <row r="60" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -5210,7 +5106,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:V64"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.33203125" customWidth="1"/>
     <col min="2" max="2" width="34.6640625" customWidth="1"/>
@@ -5231,56 +5127,56 @@
     <col min="17" max="17" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="28.8" customHeight="1">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:22" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="N1" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D1" s="9" t="s">
+      <c r="O1" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="E1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="K1" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="M1" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="N1" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="O1" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="P1" s="9" t="s">
+      <c r="P1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="Q1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="R1" s="1"/>
@@ -5289,57 +5185,57 @@
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
     </row>
-    <row r="2" spans="1:22" ht="57.6" customHeight="1">
+    <row r="2" spans="1:22" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C2" s="6" t="s">
+      <c r="M2" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="N2" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F2" s="6" t="s">
+      <c r="O2" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="P2" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="Q2" s="5" t="s">
         <v>123</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="O2" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>131</v>
       </c>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
@@ -5347,57 +5243,57 @@
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
     </row>
-    <row r="3" spans="1:22" ht="72" customHeight="1">
+    <row r="3" spans="1:22" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="O3" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="D3" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="G3" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>140</v>
-      </c>
       <c r="P3" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
@@ -5405,57 +5301,57 @@
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
     </row>
-    <row r="4" spans="1:22" ht="57.6" customHeight="1">
+    <row r="4" spans="1:22" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>142</v>
+        <v>125</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>134</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="O4" s="6" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
@@ -5463,57 +5359,57 @@
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
     </row>
-    <row r="5" spans="1:22" ht="57.6">
+    <row r="5" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>151</v>
+        <v>142</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>143</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="P5" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="Q5" s="5" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
@@ -5521,57 +5417,57 @@
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
     </row>
-    <row r="6" spans="1:22" ht="100.8" customHeight="1">
+    <row r="6" spans="1:22" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>402</v>
+        <v>385</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>404</v>
+        <v>387</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>425</v>
+        <v>408</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
@@ -5579,57 +5475,57 @@
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
     </row>
-    <row r="7" spans="1:22" ht="100.8" customHeight="1">
+    <row r="7" spans="1:22" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>417</v>
+        <v>400</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>416</v>
+        <v>399</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>418</v>
+        <v>401</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>419</v>
+        <v>402</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>420</v>
+        <v>403</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>423</v>
+        <v>406</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="P7" s="5" t="s">
-        <v>424</v>
+        <v>407</v>
       </c>
       <c r="Q7" s="5" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
@@ -5637,57 +5533,57 @@
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
     </row>
-    <row r="8" spans="1:22" ht="72" customHeight="1">
+    <row r="8" spans="1:22" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="I8" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="N8" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="J8" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="M8" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>173</v>
-      </c>
       <c r="O8" s="6" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="P8" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="Q8" s="5" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
@@ -5695,57 +5591,57 @@
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
     </row>
-    <row r="9" spans="1:22" ht="57.6" customHeight="1">
+    <row r="9" spans="1:22" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C9" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>168</v>
-      </c>
       <c r="E9" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="P9" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="Q9" s="5" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
@@ -5753,57 +5649,57 @@
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
     </row>
-    <row r="10" spans="1:22" ht="57.6" customHeight="1">
-      <c r="A10" s="13" t="s">
-        <v>25</v>
+    <row r="10" spans="1:22" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="12" t="s">
+        <v>20</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>174</v>
+        <v>70</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>166</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="J10" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="K10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="K10" s="5" t="s">
-        <v>15</v>
-      </c>
       <c r="L10" s="5" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="P10" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="Q10" s="5" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
@@ -5811,57 +5707,57 @@
       <c r="U10" s="1"/>
       <c r="V10" s="1"/>
     </row>
-    <row r="11" spans="1:22" ht="57.6" customHeight="1">
+    <row r="11" spans="1:22" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C11" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H11" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D11" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>182</v>
-      </c>
       <c r="I11" s="6" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="P11" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="Q11" s="5" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
@@ -5869,57 +5765,57 @@
       <c r="U11" s="1"/>
       <c r="V11" s="1"/>
     </row>
-    <row r="12" spans="1:22" ht="43.2" customHeight="1">
-      <c r="A12" s="13" t="s">
-        <v>19</v>
+    <row r="12" spans="1:22" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="12" t="s">
+        <v>15</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>184</v>
+        <v>166</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>176</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>459</v>
+        <v>432</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="P12" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="Q12" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
@@ -5927,57 +5823,57 @@
       <c r="U12" s="1"/>
       <c r="V12" s="1"/>
     </row>
-    <row r="13" spans="1:22" ht="43.2" customHeight="1">
+    <row r="13" spans="1:22" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>446</v>
+        <v>419</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>449</v>
+        <v>166</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>422</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>452</v>
+        <v>425</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>455</v>
+        <v>428</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>458</v>
+        <v>431</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>460</v>
+        <v>433</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="O13" s="6" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="P13" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="Q13" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
@@ -5985,57 +5881,57 @@
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
     </row>
-    <row r="14" spans="1:22" ht="43.2" customHeight="1">
-      <c r="A14" s="13" t="s">
-        <v>447</v>
+    <row r="14" spans="1:22" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="12" t="s">
+        <v>420</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="D14" s="16" t="s">
-        <v>450</v>
+        <v>166</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>423</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>453</v>
+        <v>426</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>457</v>
+        <v>430</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>458</v>
+        <v>431</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>461</v>
+        <v>434</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="P14" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="Q14" s="5" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
@@ -6043,57 +5939,57 @@
       <c r="U14" s="1"/>
       <c r="V14" s="1"/>
     </row>
-    <row r="15" spans="1:22" ht="43.2" customHeight="1">
+    <row r="15" spans="1:22" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>448</v>
+        <v>421</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="D15" s="16" t="s">
-        <v>451</v>
+        <v>166</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>424</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>454</v>
+        <v>427</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>456</v>
+        <v>429</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>458</v>
+        <v>431</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>462</v>
+        <v>435</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="P15" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
@@ -6101,57 +5997,57 @@
       <c r="U15" s="1"/>
       <c r="V15" s="1"/>
     </row>
-    <row r="16" spans="1:22" ht="43.2" customHeight="1">
+    <row r="16" spans="1:22" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="M16" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C16" s="6" t="s">
+      <c r="N16" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="O16" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="K16" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="L16" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="M16" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="N16" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="O16" s="6" t="s">
-        <v>199</v>
-      </c>
       <c r="P16" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="Q16" s="5" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
@@ -6159,57 +6055,57 @@
       <c r="U16" s="1"/>
       <c r="V16" s="1"/>
     </row>
-    <row r="17" spans="1:22" ht="72" customHeight="1">
+    <row r="17" spans="1:22" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="M17" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="N17" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="K17" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="L17" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="M17" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="N17" s="6" t="s">
-        <v>208</v>
-      </c>
       <c r="O17" s="6" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="P17" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="Q17" s="5" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
@@ -6217,57 +6113,57 @@
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
     </row>
-    <row r="18" spans="1:22" ht="57.6" customHeight="1">
-      <c r="A18" s="13" t="s">
+    <row r="18" spans="1:22" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="N18" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="O18" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="K18" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="L18" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="M18" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="N18" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="O18" s="6" t="s">
-        <v>217</v>
-      </c>
       <c r="P18" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="Q18" s="5" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
@@ -6275,57 +6171,57 @@
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
     </row>
-    <row r="19" spans="1:22" ht="43.2" customHeight="1">
+    <row r="19" spans="1:22" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="M19" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="C19" s="6" t="s">
+      <c r="N19" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="D19" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="J19" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="K19" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="L19" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="M19" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="N19" s="6" t="s">
-        <v>227</v>
-      </c>
       <c r="O19" s="6" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="P19" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="Q19" s="5" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
@@ -6333,57 +6229,57 @@
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
     </row>
-    <row r="20" spans="1:22" ht="43.2" customHeight="1">
+    <row r="20" spans="1:22" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="L20" s="5" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="P20" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="Q20" s="5" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
@@ -6391,57 +6287,57 @@
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
     </row>
-    <row r="21" spans="1:22" ht="43.2" customHeight="1">
+    <row r="21" spans="1:22" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="F21" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="G21" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="G21" s="6" t="s">
-        <v>238</v>
-      </c>
       <c r="H21" s="6" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="P21" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="Q21" s="5" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
@@ -6449,57 +6345,57 @@
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
     </row>
-    <row r="22" spans="1:22" ht="43.2" customHeight="1">
+    <row r="22" spans="1:22" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="M22" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="C22" s="6" t="s">
+      <c r="N22" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="K22" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="L22" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="M22" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="N22" s="6" t="s">
-        <v>250</v>
-      </c>
       <c r="O22" s="6" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="P22" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="Q22" s="5" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
@@ -6507,57 +6403,57 @@
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
     </row>
-    <row r="23" spans="1:22" ht="57.6" customHeight="1">
+    <row r="23" spans="1:22" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="J23" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="D23" s="16" t="s">
-        <v>252</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="J23" s="6" t="s">
+      <c r="K23" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="K23" s="5" t="s">
-        <v>15</v>
-      </c>
       <c r="L23" s="5" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="N23" s="6" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="O23" s="6" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="P23" s="5" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="Q23" s="5" t="s">
-        <v>463</v>
+        <v>436</v>
       </c>
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
@@ -6565,57 +6461,57 @@
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
     </row>
-    <row r="24" spans="1:22" ht="115.2" customHeight="1">
+    <row r="24" spans="1:22" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="L24" s="5" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="P24" s="5" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="Q24" s="5" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
@@ -6623,57 +6519,57 @@
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
     </row>
-    <row r="25" spans="1:22" ht="158.4" customHeight="1">
+    <row r="25" spans="1:22" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C25" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="M25" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="N25" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="J25" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="K25" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="L25" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="M25" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="N25" s="6" t="s">
-        <v>250</v>
-      </c>
       <c r="O25" s="6" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="P25" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="Q25" s="5" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
@@ -6681,57 +6577,57 @@
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
     </row>
-    <row r="26" spans="1:22" ht="115.2">
+    <row r="26" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="M26" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="N26" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="O26" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="K26" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="L26" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="M26" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="N26" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="O26" s="6" t="s">
-        <v>278</v>
-      </c>
       <c r="P26" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="Q26" s="5" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
@@ -6739,57 +6635,57 @@
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
     </row>
-    <row r="27" spans="1:22" ht="115.2">
+    <row r="27" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>409</v>
+        <v>392</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="L27" s="5" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="N27" s="6" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="O27" s="6" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="P27" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="Q27" s="5" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
@@ -6797,7 +6693,7 @@
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
     </row>
-    <row r="28" spans="1:22">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -6821,7 +6717,7 @@
       <c r="U28" s="1"/>
       <c r="V28" s="1"/>
     </row>
-    <row r="29" spans="1:22">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -6845,7 +6741,7 @@
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
     </row>
-    <row r="30" spans="1:22">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -6869,7 +6765,7 @@
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
     </row>
-    <row r="31" spans="1:22">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -6893,7 +6789,7 @@
       <c r="U31" s="1"/>
       <c r="V31" s="1"/>
     </row>
-    <row r="32" spans="1:22">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -6917,7 +6813,7 @@
       <c r="U32" s="1"/>
       <c r="V32" s="1"/>
     </row>
-    <row r="33" spans="1:22">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -6941,7 +6837,7 @@
       <c r="U33" s="1"/>
       <c r="V33" s="1"/>
     </row>
-    <row r="34" spans="1:22">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -6965,7 +6861,7 @@
       <c r="U34" s="1"/>
       <c r="V34" s="1"/>
     </row>
-    <row r="35" spans="1:22">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -6989,7 +6885,7 @@
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
     </row>
-    <row r="36" spans="1:22">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -7013,7 +6909,7 @@
       <c r="U36" s="1"/>
       <c r="V36" s="1"/>
     </row>
-    <row r="37" spans="1:22">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -7037,7 +6933,7 @@
       <c r="U37" s="1"/>
       <c r="V37" s="1"/>
     </row>
-    <row r="38" spans="1:22">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -7061,7 +6957,7 @@
       <c r="U38" s="1"/>
       <c r="V38" s="1"/>
     </row>
-    <row r="39" spans="1:22">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -7085,7 +6981,7 @@
       <c r="U39" s="1"/>
       <c r="V39" s="1"/>
     </row>
-    <row r="40" spans="1:22">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -7109,7 +7005,7 @@
       <c r="U40" s="1"/>
       <c r="V40" s="1"/>
     </row>
-    <row r="41" spans="1:22">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -7133,7 +7029,7 @@
       <c r="U41" s="1"/>
       <c r="V41" s="1"/>
     </row>
-    <row r="42" spans="1:22">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -7157,7 +7053,7 @@
       <c r="U42" s="1"/>
       <c r="V42" s="1"/>
     </row>
-    <row r="43" spans="1:22">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -7181,7 +7077,7 @@
       <c r="U43" s="1"/>
       <c r="V43" s="1"/>
     </row>
-    <row r="44" spans="1:22">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -7205,7 +7101,7 @@
       <c r="U44" s="1"/>
       <c r="V44" s="1"/>
     </row>
-    <row r="45" spans="1:22">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -7229,7 +7125,7 @@
       <c r="U45" s="1"/>
       <c r="V45" s="1"/>
     </row>
-    <row r="46" spans="1:22">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -7253,7 +7149,7 @@
       <c r="U46" s="1"/>
       <c r="V46" s="1"/>
     </row>
-    <row r="47" spans="1:22">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -7277,7 +7173,7 @@
       <c r="U47" s="1"/>
       <c r="V47" s="1"/>
     </row>
-    <row r="48" spans="1:22">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -7301,7 +7197,7 @@
       <c r="U48" s="1"/>
       <c r="V48" s="1"/>
     </row>
-    <row r="49" spans="1:22">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -7325,7 +7221,7 @@
       <c r="U49" s="1"/>
       <c r="V49" s="1"/>
     </row>
-    <row r="50" spans="1:22">
+    <row r="50" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -7349,7 +7245,7 @@
       <c r="U50" s="1"/>
       <c r="V50" s="1"/>
     </row>
-    <row r="51" spans="1:22">
+    <row r="51" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -7373,7 +7269,7 @@
       <c r="U51" s="1"/>
       <c r="V51" s="1"/>
     </row>
-    <row r="52" spans="1:22">
+    <row r="52" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -7397,7 +7293,7 @@
       <c r="U52" s="1"/>
       <c r="V52" s="1"/>
     </row>
-    <row r="53" spans="1:22">
+    <row r="53" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -7421,7 +7317,7 @@
       <c r="U53" s="1"/>
       <c r="V53" s="1"/>
     </row>
-    <row r="54" spans="1:22">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -7445,7 +7341,7 @@
       <c r="U54" s="1"/>
       <c r="V54" s="1"/>
     </row>
-    <row r="55" spans="1:22">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -7469,7 +7365,7 @@
       <c r="U55" s="1"/>
       <c r="V55" s="1"/>
     </row>
-    <row r="56" spans="1:22">
+    <row r="56" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -7493,7 +7389,7 @@
       <c r="U56" s="1"/>
       <c r="V56" s="1"/>
     </row>
-    <row r="57" spans="1:22">
+    <row r="57" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -7517,7 +7413,7 @@
       <c r="U57" s="1"/>
       <c r="V57" s="1"/>
     </row>
-    <row r="58" spans="1:22">
+    <row r="58" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -7541,7 +7437,7 @@
       <c r="U58" s="1"/>
       <c r="V58" s="1"/>
     </row>
-    <row r="59" spans="1:22">
+    <row r="59" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -7565,7 +7461,7 @@
       <c r="U59" s="1"/>
       <c r="V59" s="1"/>
     </row>
-    <row r="60" spans="1:22">
+    <row r="60" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -7589,7 +7485,7 @@
       <c r="U60" s="1"/>
       <c r="V60" s="1"/>
     </row>
-    <row r="61" spans="1:22">
+    <row r="61" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -7613,7 +7509,7 @@
       <c r="U61" s="1"/>
       <c r="V61" s="1"/>
     </row>
-    <row r="62" spans="1:22">
+    <row r="62" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -7637,7 +7533,7 @@
       <c r="U62" s="1"/>
       <c r="V62" s="1"/>
     </row>
-    <row r="63" spans="1:22">
+    <row r="63" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -7661,7 +7557,7 @@
       <c r="U63" s="1"/>
       <c r="V63" s="1"/>
     </row>
-    <row r="64" spans="1:22">
+    <row r="64" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -7686,7 +7582,7 @@
       <c r="V64" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7694,7 +7590,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:V60"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="35" customWidth="1"/>
@@ -7703,21 +7599,21 @@
     <col min="5" max="5" width="26.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
-      <c r="A1" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>285</v>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>277</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -7737,21 +7633,21 @@
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
     </row>
-    <row r="2" spans="1:22" ht="28.8" customHeight="1">
+    <row r="2" spans="1:22" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
@@ -7771,21 +7667,21 @@
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
@@ -7805,21 +7701,21 @@
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
@@ -7839,21 +7735,21 @@
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
     </row>
-    <row r="5" spans="1:22">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
@@ -7873,21 +7769,21 @@
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
     </row>
-    <row r="6" spans="1:22" ht="28.8" customHeight="1">
+    <row r="6" spans="1:22" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
@@ -7907,21 +7803,21 @@
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
     </row>
-    <row r="7" spans="1:22" ht="28.8">
+    <row r="7" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
@@ -7941,21 +7837,21 @@
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
     </row>
-    <row r="8" spans="1:22" ht="28.8">
+    <row r="8" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
@@ -7975,21 +7871,21 @@
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
     </row>
-    <row r="9" spans="1:22" ht="43.2">
+    <row r="9" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
@@ -8009,21 +7905,21 @@
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
     </row>
-    <row r="10" spans="1:22" ht="43.2">
+    <row r="10" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>401</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>464</v>
+        <v>384</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>446</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
@@ -8043,7 +7939,7 @@
       <c r="U10" s="1"/>
       <c r="V10" s="1"/>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -8067,7 +7963,7 @@
       <c r="U11" s="1"/>
       <c r="V11" s="1"/>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -8091,7 +7987,7 @@
       <c r="U12" s="1"/>
       <c r="V12" s="1"/>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -8115,7 +8011,7 @@
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -8139,7 +8035,7 @@
       <c r="U14" s="1"/>
       <c r="V14" s="1"/>
     </row>
-    <row r="15" spans="1:22">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -8163,7 +8059,7 @@
       <c r="U15" s="1"/>
       <c r="V15" s="1"/>
     </row>
-    <row r="16" spans="1:22">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -8187,7 +8083,7 @@
       <c r="U16" s="1"/>
       <c r="V16" s="1"/>
     </row>
-    <row r="17" spans="1:22">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -8211,7 +8107,7 @@
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
     </row>
-    <row r="18" spans="1:22">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -8235,7 +8131,7 @@
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
     </row>
-    <row r="19" spans="1:22">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -8259,7 +8155,7 @@
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
     </row>
-    <row r="20" spans="1:22">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -8283,7 +8179,7 @@
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
     </row>
-    <row r="21" spans="1:22">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -8307,7 +8203,7 @@
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
     </row>
-    <row r="22" spans="1:22">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -8331,7 +8227,7 @@
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
     </row>
-    <row r="23" spans="1:22">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -8355,7 +8251,7 @@
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
     </row>
-    <row r="24" spans="1:22">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -8379,7 +8275,7 @@
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
     </row>
-    <row r="25" spans="1:22">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -8403,7 +8299,7 @@
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
     </row>
-    <row r="26" spans="1:22">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -8427,7 +8323,7 @@
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
     </row>
-    <row r="27" spans="1:22">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -8451,7 +8347,7 @@
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
     </row>
-    <row r="28" spans="1:22">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -8475,7 +8371,7 @@
       <c r="U28" s="1"/>
       <c r="V28" s="1"/>
     </row>
-    <row r="29" spans="1:22">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -8499,7 +8395,7 @@
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
     </row>
-    <row r="30" spans="1:22">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -8523,7 +8419,7 @@
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
     </row>
-    <row r="31" spans="1:22">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -8547,7 +8443,7 @@
       <c r="U31" s="1"/>
       <c r="V31" s="1"/>
     </row>
-    <row r="32" spans="1:22">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -8571,7 +8467,7 @@
       <c r="U32" s="1"/>
       <c r="V32" s="1"/>
     </row>
-    <row r="33" spans="1:22">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -8595,7 +8491,7 @@
       <c r="U33" s="1"/>
       <c r="V33" s="1"/>
     </row>
-    <row r="34" spans="1:22">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -8619,7 +8515,7 @@
       <c r="U34" s="1"/>
       <c r="V34" s="1"/>
     </row>
-    <row r="35" spans="1:22">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -8643,7 +8539,7 @@
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
     </row>
-    <row r="36" spans="1:22">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -8667,7 +8563,7 @@
       <c r="U36" s="1"/>
       <c r="V36" s="1"/>
     </row>
-    <row r="37" spans="1:22">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -8691,7 +8587,7 @@
       <c r="U37" s="1"/>
       <c r="V37" s="1"/>
     </row>
-    <row r="38" spans="1:22">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -8715,7 +8611,7 @@
       <c r="U38" s="1"/>
       <c r="V38" s="1"/>
     </row>
-    <row r="39" spans="1:22">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -8739,7 +8635,7 @@
       <c r="U39" s="1"/>
       <c r="V39" s="1"/>
     </row>
-    <row r="40" spans="1:22">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -8763,7 +8659,7 @@
       <c r="U40" s="1"/>
       <c r="V40" s="1"/>
     </row>
-    <row r="41" spans="1:22">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -8787,7 +8683,7 @@
       <c r="U41" s="1"/>
       <c r="V41" s="1"/>
     </row>
-    <row r="42" spans="1:22">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -8811,7 +8707,7 @@
       <c r="U42" s="1"/>
       <c r="V42" s="1"/>
     </row>
-    <row r="43" spans="1:22">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -8835,7 +8731,7 @@
       <c r="U43" s="1"/>
       <c r="V43" s="1"/>
     </row>
-    <row r="44" spans="1:22">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -8859,7 +8755,7 @@
       <c r="U44" s="1"/>
       <c r="V44" s="1"/>
     </row>
-    <row r="45" spans="1:22">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -8883,7 +8779,7 @@
       <c r="U45" s="1"/>
       <c r="V45" s="1"/>
     </row>
-    <row r="46" spans="1:22">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -8907,7 +8803,7 @@
       <c r="U46" s="1"/>
       <c r="V46" s="1"/>
     </row>
-    <row r="47" spans="1:22">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -8931,7 +8827,7 @@
       <c r="U47" s="1"/>
       <c r="V47" s="1"/>
     </row>
-    <row r="48" spans="1:22">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -8955,7 +8851,7 @@
       <c r="U48" s="1"/>
       <c r="V48" s="1"/>
     </row>
-    <row r="49" spans="1:22">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -8979,7 +8875,7 @@
       <c r="U49" s="1"/>
       <c r="V49" s="1"/>
     </row>
-    <row r="50" spans="1:22">
+    <row r="50" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -9003,7 +8899,7 @@
       <c r="U50" s="1"/>
       <c r="V50" s="1"/>
     </row>
-    <row r="51" spans="1:22">
+    <row r="51" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -9027,7 +8923,7 @@
       <c r="U51" s="1"/>
       <c r="V51" s="1"/>
     </row>
-    <row r="52" spans="1:22">
+    <row r="52" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -9051,7 +8947,7 @@
       <c r="U52" s="1"/>
       <c r="V52" s="1"/>
     </row>
-    <row r="53" spans="1:22">
+    <row r="53" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -9075,7 +8971,7 @@
       <c r="U53" s="1"/>
       <c r="V53" s="1"/>
     </row>
-    <row r="54" spans="1:22">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -9099,7 +8995,7 @@
       <c r="U54" s="1"/>
       <c r="V54" s="1"/>
     </row>
-    <row r="55" spans="1:22">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -9123,7 +9019,7 @@
       <c r="U55" s="1"/>
       <c r="V55" s="1"/>
     </row>
-    <row r="56" spans="1:22">
+    <row r="56" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -9147,7 +9043,7 @@
       <c r="U56" s="1"/>
       <c r="V56" s="1"/>
     </row>
-    <row r="57" spans="1:22">
+    <row r="57" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -9171,7 +9067,7 @@
       <c r="U57" s="1"/>
       <c r="V57" s="1"/>
     </row>
-    <row r="58" spans="1:22">
+    <row r="58" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -9195,7 +9091,7 @@
       <c r="U58" s="1"/>
       <c r="V58" s="1"/>
     </row>
-    <row r="59" spans="1:22">
+    <row r="59" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -9219,7 +9115,7 @@
       <c r="U59" s="1"/>
       <c r="V59" s="1"/>
     </row>
-    <row r="60" spans="1:22">
+    <row r="60" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -9244,15 +9140,15 @@
       <c r="V60" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:U64"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:T64"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="58.88671875" customWidth="1"/>
@@ -9260,19 +9156,18 @@
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
-      <c r="A1" s="21" t="s">
-        <v>312</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A1" s="25" t="s">
+        <v>304</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -9286,9 +9181,8 @@
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-    </row>
-    <row r="2" spans="1:21">
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -9309,14 +9203,13 @@
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
-    </row>
-    <row r="3" spans="1:21">
-      <c r="A3" s="10" t="s">
-        <v>313</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>426</v>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>409</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -9336,14 +9229,13 @@
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
-      <c r="U3" s="1"/>
-    </row>
-    <row r="4" spans="1:21">
-      <c r="A4" s="10" t="s">
-        <v>314</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>427</v>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>410</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -9363,14 +9255,13 @@
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
-      <c r="U4" s="1"/>
-    </row>
-    <row r="5" spans="1:21">
-      <c r="A5" s="10" t="s">
-        <v>315</v>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
+        <v>307</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -9390,14 +9281,13 @@
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
-      <c r="U5" s="1"/>
-    </row>
-    <row r="6" spans="1:21">
-      <c r="A6" s="10" t="s">
-        <v>317</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>428</v>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>411</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -9417,11 +9307,10 @@
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
-      <c r="U6" s="1"/>
-    </row>
-    <row r="7" spans="1:21">
-      <c r="A7" s="10" t="s">
-        <v>318</v>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>310</v>
       </c>
       <c r="B7" s="1">
         <v>26</v>
@@ -9444,11 +9333,10 @@
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
       <c r="T7" s="1"/>
-      <c r="U7" s="1"/>
-    </row>
-    <row r="8" spans="1:21">
-      <c r="A8" s="10" t="s">
-        <v>130</v>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>122</v>
       </c>
       <c r="B8" s="1">
         <v>26</v>
@@ -9471,11 +9359,10 @@
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
-      <c r="U8" s="1"/>
-    </row>
-    <row r="9" spans="1:21">
-      <c r="A9" s="10" t="s">
-        <v>158</v>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
+        <v>150</v>
       </c>
       <c r="B9" s="1">
         <v>0</v>
@@ -9498,11 +9385,10 @@
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
-      <c r="U9" s="1"/>
-    </row>
-    <row r="10" spans="1:21">
-      <c r="A10" s="10" t="s">
-        <v>319</v>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
+        <v>311</v>
       </c>
       <c r="B10" s="1">
         <v>0</v>
@@ -9525,11 +9411,10 @@
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
-      <c r="U10" s="1"/>
-    </row>
-    <row r="11" spans="1:21">
-      <c r="A11" s="10" t="s">
-        <v>320</v>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A11" s="9" t="s">
+        <v>312</v>
       </c>
       <c r="B11" s="1">
         <f>B8/B7</f>
@@ -9553,9 +9438,8 @@
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
-      <c r="U11" s="1"/>
-    </row>
-    <row r="12" spans="1:21">
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -9576,30 +9460,27 @@
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
-      <c r="U12" s="1"/>
-    </row>
-    <row r="13" spans="1:21">
-      <c r="A13" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>321</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="E13" s="9" t="s">
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="E13" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F13" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="G13" s="9" t="s">
-        <v>9</v>
-      </c>
+      <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -9613,30 +9494,27 @@
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
       <c r="T13" s="1"/>
-      <c r="U13" s="1"/>
-    </row>
-    <row r="14" spans="1:21" ht="43.2">
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="G14" s="20" t="s">
-        <v>439</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -9650,30 +9528,27 @@
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
-      <c r="U14" s="1"/>
-    </row>
-    <row r="15" spans="1:21" ht="28.8" customHeight="1">
+    </row>
+    <row r="15" spans="1:20" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="G15" s="20" t="s">
-        <v>435</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -9687,30 +9562,27 @@
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
-      <c r="U15" s="1"/>
-    </row>
-    <row r="16" spans="1:21" ht="28.8" customHeight="1">
+    </row>
+    <row r="16" spans="1:20" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="G16" s="20" t="s">
-        <v>436</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -9724,30 +9596,27 @@
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
-      <c r="U16" s="1"/>
-    </row>
-    <row r="17" spans="1:21" ht="28.8" customHeight="1">
+    </row>
+    <row r="17" spans="1:20" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>324</v>
-      </c>
-      <c r="G17" s="20" t="s">
-        <v>437</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -9761,30 +9630,27 @@
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
-      <c r="U17" s="1"/>
-    </row>
-    <row r="18" spans="1:21" ht="28.8" customHeight="1">
+    </row>
+    <row r="18" spans="1:20" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>156</v>
+        <v>26</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>148</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>324</v>
-      </c>
-      <c r="G18" s="20" t="s">
-        <v>438</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
@@ -9798,26 +9664,25 @@
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
       <c r="T18" s="1"/>
-      <c r="U18" s="1"/>
-    </row>
-    <row r="19" spans="1:21" ht="28.8" customHeight="1">
-      <c r="A19" s="13" t="s">
-        <v>412</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>445</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>323</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="F19" s="13"/>
-      <c r="G19" s="20"/>
+    </row>
+    <row r="19" spans="1:20" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>418</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="F19" s="12"/>
+      <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -9831,30 +9696,27 @@
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
-      <c r="U19" s="1"/>
-    </row>
-    <row r="20" spans="1:21" ht="28.8" customHeight="1">
+    </row>
+    <row r="20" spans="1:20" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="G20" s="20" t="s">
-        <v>440</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -9868,30 +9730,27 @@
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
-      <c r="U20" s="1"/>
-    </row>
-    <row r="21" spans="1:21" ht="28.8" customHeight="1">
+    </row>
+    <row r="21" spans="1:20" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="G21" s="20" t="s">
-        <v>441</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -9905,30 +9764,27 @@
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
       <c r="T21" s="1"/>
-      <c r="U21" s="1"/>
-    </row>
-    <row r="22" spans="1:21" ht="28.8" customHeight="1">
+    </row>
+    <row r="22" spans="1:20" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>429</v>
+        <v>315</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>412</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="G22" s="20" t="s">
-        <v>442</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -9942,30 +9798,27 @@
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
-      <c r="U22" s="1"/>
-    </row>
-    <row r="23" spans="1:21" ht="28.8" customHeight="1">
+    </row>
+    <row r="23" spans="1:20" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B23" s="16" t="s">
-        <v>180</v>
+        <v>27</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>172</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>130</v>
+        <v>315</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>122</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="G23" s="20" t="s">
-        <v>443</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
@@ -9979,30 +9832,27 @@
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
-      <c r="U23" s="1"/>
-    </row>
-    <row r="24" spans="1:21" ht="28.8" customHeight="1">
+    </row>
+    <row r="24" spans="1:20" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="F24" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="G24" s="20" t="s">
-        <v>444</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
@@ -10016,28 +9866,27 @@
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
       <c r="T24" s="1"/>
-      <c r="U24" s="1"/>
-    </row>
-    <row r="25" spans="1:21" ht="28.8" customHeight="1">
+    </row>
+    <row r="25" spans="1:20" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>446</v>
+        <v>419</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>465</v>
+        <v>437</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="F25" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G25" s="20"/>
+        <v>315</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
@@ -10051,28 +9900,27 @@
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
       <c r="T25" s="1"/>
-      <c r="U25" s="1"/>
-    </row>
-    <row r="26" spans="1:21" ht="28.8" customHeight="1">
+    </row>
+    <row r="26" spans="1:20" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>447</v>
+        <v>420</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>450</v>
+        <v>423</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="F26" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="G26" s="20"/>
+        <v>315</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
@@ -10086,28 +9934,27 @@
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
       <c r="T26" s="1"/>
-      <c r="U26" s="1"/>
-    </row>
-    <row r="27" spans="1:21" ht="28.8" customHeight="1">
+    </row>
+    <row r="27" spans="1:20" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
-        <v>448</v>
+        <v>421</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>451</v>
+        <v>424</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="G27" s="20"/>
+        <v>315</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
@@ -10121,30 +9968,27 @@
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
       <c r="T27" s="1"/>
-      <c r="U27" s="1"/>
-    </row>
-    <row r="28" spans="1:21" ht="28.8" customHeight="1">
+    </row>
+    <row r="28" spans="1:20" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>324</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>325</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
@@ -10158,30 +10002,27 @@
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
       <c r="T28" s="1"/>
-      <c r="U28" s="1"/>
-    </row>
-    <row r="29" spans="1:21" ht="28.8" customHeight="1">
+    </row>
+    <row r="29" spans="1:20" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>326</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
@@ -10195,30 +10036,27 @@
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
       <c r="T29" s="1"/>
-      <c r="U29" s="1"/>
-    </row>
-    <row r="30" spans="1:21" ht="28.8">
+    </row>
+    <row r="30" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>324</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>327</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="F30" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
@@ -10232,30 +10070,27 @@
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="1"/>
-      <c r="U30" s="1"/>
-    </row>
-    <row r="31" spans="1:21" ht="28.8" customHeight="1">
+    </row>
+    <row r="31" spans="1:20" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>328</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
@@ -10269,30 +10104,27 @@
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
       <c r="T31" s="1"/>
-      <c r="U31" s="1"/>
-    </row>
-    <row r="32" spans="1:21" ht="28.8" customHeight="1">
+    </row>
+    <row r="32" spans="1:20" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="G32" s="7" t="s">
-        <v>329</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
@@ -10306,30 +10138,27 @@
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
       <c r="T32" s="1"/>
-      <c r="U32" s="1"/>
-    </row>
-    <row r="33" spans="1:21" ht="28.8" customHeight="1">
+    </row>
+    <row r="33" spans="1:20" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>330</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="G33" s="1"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
@@ -10343,30 +10172,27 @@
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
       <c r="T33" s="1"/>
-      <c r="U33" s="1"/>
-    </row>
-    <row r="34" spans="1:21" ht="28.8" customHeight="1">
+    </row>
+    <row r="34" spans="1:20" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>331</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
@@ -10380,30 +10206,27 @@
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
       <c r="T34" s="1"/>
-      <c r="U34" s="1"/>
-    </row>
-    <row r="35" spans="1:21" ht="28.8" customHeight="1">
+    </row>
+    <row r="35" spans="1:20" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="E35" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="F35" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>17</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="G35" s="1"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
@@ -10417,30 +10240,27 @@
       <c r="R35" s="1"/>
       <c r="S35" s="1"/>
       <c r="T35" s="1"/>
-      <c r="U35" s="1"/>
-    </row>
-    <row r="36" spans="1:21" ht="28.8" customHeight="1">
+    </row>
+    <row r="36" spans="1:20" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="E36" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="F36" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="G36" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="E36" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="F36" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G36" s="1"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
@@ -10454,30 +10274,27 @@
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
       <c r="T36" s="1"/>
-      <c r="U36" s="1"/>
-    </row>
-    <row r="37" spans="1:21" ht="28.8" customHeight="1">
+    </row>
+    <row r="37" spans="1:20" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="G37" s="7" t="s">
-        <v>331</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="G37" s="1"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
@@ -10491,30 +10308,27 @@
       <c r="R37" s="1"/>
       <c r="S37" s="1"/>
       <c r="T37" s="1"/>
-      <c r="U37" s="1"/>
-    </row>
-    <row r="38" spans="1:21" ht="28.8">
+    </row>
+    <row r="38" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="G38" s="7" t="s">
-        <v>332</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="G38" s="1"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
@@ -10528,30 +10342,27 @@
       <c r="R38" s="1"/>
       <c r="S38" s="1"/>
       <c r="T38" s="1"/>
-      <c r="U38" s="1"/>
-    </row>
-    <row r="39" spans="1:21" ht="28.8">
+    </row>
+    <row r="39" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="G39" s="7" t="s">
-        <v>333</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="G39" s="1"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
@@ -10565,9 +10376,8 @@
       <c r="R39" s="1"/>
       <c r="S39" s="1"/>
       <c r="T39" s="1"/>
-      <c r="U39" s="1"/>
-    </row>
-    <row r="40" spans="1:21">
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -10588,9 +10398,8 @@
       <c r="R40" s="1"/>
       <c r="S40" s="1"/>
       <c r="T40" s="1"/>
-      <c r="U40" s="1"/>
-    </row>
-    <row r="41" spans="1:21">
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -10611,9 +10420,8 @@
       <c r="R41" s="1"/>
       <c r="S41" s="1"/>
       <c r="T41" s="1"/>
-      <c r="U41" s="1"/>
-    </row>
-    <row r="42" spans="1:21">
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -10634,9 +10442,8 @@
       <c r="R42" s="1"/>
       <c r="S42" s="1"/>
       <c r="T42" s="1"/>
-      <c r="U42" s="1"/>
-    </row>
-    <row r="43" spans="1:21">
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -10657,9 +10464,8 @@
       <c r="R43" s="1"/>
       <c r="S43" s="1"/>
       <c r="T43" s="1"/>
-      <c r="U43" s="1"/>
-    </row>
-    <row r="44" spans="1:21">
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -10680,9 +10486,8 @@
       <c r="R44" s="1"/>
       <c r="S44" s="1"/>
       <c r="T44" s="1"/>
-      <c r="U44" s="1"/>
-    </row>
-    <row r="45" spans="1:21">
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -10703,9 +10508,8 @@
       <c r="R45" s="1"/>
       <c r="S45" s="1"/>
       <c r="T45" s="1"/>
-      <c r="U45" s="1"/>
-    </row>
-    <row r="46" spans="1:21">
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -10726,9 +10530,8 @@
       <c r="R46" s="1"/>
       <c r="S46" s="1"/>
       <c r="T46" s="1"/>
-      <c r="U46" s="1"/>
-    </row>
-    <row r="47" spans="1:21">
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -10749,9 +10552,8 @@
       <c r="R47" s="1"/>
       <c r="S47" s="1"/>
       <c r="T47" s="1"/>
-      <c r="U47" s="1"/>
-    </row>
-    <row r="48" spans="1:21">
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -10772,9 +10574,8 @@
       <c r="R48" s="1"/>
       <c r="S48" s="1"/>
       <c r="T48" s="1"/>
-      <c r="U48" s="1"/>
-    </row>
-    <row r="49" spans="1:21">
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -10795,9 +10596,8 @@
       <c r="R49" s="1"/>
       <c r="S49" s="1"/>
       <c r="T49" s="1"/>
-      <c r="U49" s="1"/>
-    </row>
-    <row r="50" spans="1:21">
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -10818,9 +10618,8 @@
       <c r="R50" s="1"/>
       <c r="S50" s="1"/>
       <c r="T50" s="1"/>
-      <c r="U50" s="1"/>
-    </row>
-    <row r="51" spans="1:21">
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -10841,9 +10640,8 @@
       <c r="R51" s="1"/>
       <c r="S51" s="1"/>
       <c r="T51" s="1"/>
-      <c r="U51" s="1"/>
-    </row>
-    <row r="52" spans="1:21">
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -10864,9 +10662,8 @@
       <c r="R52" s="1"/>
       <c r="S52" s="1"/>
       <c r="T52" s="1"/>
-      <c r="U52" s="1"/>
-    </row>
-    <row r="53" spans="1:21">
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -10887,9 +10684,8 @@
       <c r="R53" s="1"/>
       <c r="S53" s="1"/>
       <c r="T53" s="1"/>
-      <c r="U53" s="1"/>
-    </row>
-    <row r="54" spans="1:21">
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -10910,9 +10706,8 @@
       <c r="R54" s="1"/>
       <c r="S54" s="1"/>
       <c r="T54" s="1"/>
-      <c r="U54" s="1"/>
-    </row>
-    <row r="55" spans="1:21">
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -10933,9 +10728,8 @@
       <c r="R55" s="1"/>
       <c r="S55" s="1"/>
       <c r="T55" s="1"/>
-      <c r="U55" s="1"/>
-    </row>
-    <row r="56" spans="1:21">
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -10956,9 +10750,8 @@
       <c r="R56" s="1"/>
       <c r="S56" s="1"/>
       <c r="T56" s="1"/>
-      <c r="U56" s="1"/>
-    </row>
-    <row r="57" spans="1:21">
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -10979,9 +10772,8 @@
       <c r="R57" s="1"/>
       <c r="S57" s="1"/>
       <c r="T57" s="1"/>
-      <c r="U57" s="1"/>
-    </row>
-    <row r="58" spans="1:21">
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -11002,9 +10794,8 @@
       <c r="R58" s="1"/>
       <c r="S58" s="1"/>
       <c r="T58" s="1"/>
-      <c r="U58" s="1"/>
-    </row>
-    <row r="59" spans="1:21">
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -11025,9 +10816,8 @@
       <c r="R59" s="1"/>
       <c r="S59" s="1"/>
       <c r="T59" s="1"/>
-      <c r="U59" s="1"/>
-    </row>
-    <row r="60" spans="1:21">
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -11048,9 +10838,8 @@
       <c r="R60" s="1"/>
       <c r="S60" s="1"/>
       <c r="T60" s="1"/>
-      <c r="U60" s="1"/>
-    </row>
-    <row r="61" spans="1:21">
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -11071,9 +10860,8 @@
       <c r="R61" s="1"/>
       <c r="S61" s="1"/>
       <c r="T61" s="1"/>
-      <c r="U61" s="1"/>
-    </row>
-    <row r="62" spans="1:21">
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -11094,9 +10882,8 @@
       <c r="R62" s="1"/>
       <c r="S62" s="1"/>
       <c r="T62" s="1"/>
-      <c r="U62" s="1"/>
-    </row>
-    <row r="63" spans="1:21">
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -11117,9 +10904,8 @@
       <c r="R63" s="1"/>
       <c r="S63" s="1"/>
       <c r="T63" s="1"/>
-      <c r="U63" s="1"/>
-    </row>
-    <row r="64" spans="1:21">
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -11140,45 +10926,20 @@
       <c r="R64" s="1"/>
       <c r="S64" s="1"/>
       <c r="T64" s="1"/>
-      <c r="U64" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="G14" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
-    <hyperlink ref="G15" r:id="rId2" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
-    <hyperlink ref="G16" r:id="rId3" xr:uid="{00000000-0004-0000-0400-000002000000}"/>
-    <hyperlink ref="G17" r:id="rId4" xr:uid="{00000000-0004-0000-0400-000003000000}"/>
-    <hyperlink ref="G18" r:id="rId5" xr:uid="{00000000-0004-0000-0400-000004000000}"/>
-    <hyperlink ref="G20" r:id="rId6" xr:uid="{00000000-0004-0000-0400-000005000000}"/>
-    <hyperlink ref="G21" r:id="rId7" xr:uid="{00000000-0004-0000-0400-000006000000}"/>
-    <hyperlink ref="G22" r:id="rId8" xr:uid="{00000000-0004-0000-0400-000007000000}"/>
-    <hyperlink ref="G23" r:id="rId9" xr:uid="{00000000-0004-0000-0400-000008000000}"/>
-    <hyperlink ref="G24" r:id="rId10" xr:uid="{00000000-0004-0000-0400-000009000000}"/>
-    <hyperlink ref="G28" r:id="rId11" xr:uid="{00000000-0004-0000-0400-00000A000000}"/>
-    <hyperlink ref="G29" r:id="rId12" xr:uid="{00000000-0004-0000-0400-00000B000000}"/>
-    <hyperlink ref="G30" r:id="rId13" xr:uid="{00000000-0004-0000-0400-00000C000000}"/>
-    <hyperlink ref="G31" r:id="rId14" xr:uid="{00000000-0004-0000-0400-00000D000000}"/>
-    <hyperlink ref="G32" r:id="rId15" xr:uid="{00000000-0004-0000-0400-00000E000000}"/>
-    <hyperlink ref="G33" r:id="rId16" xr:uid="{00000000-0004-0000-0400-00000F000000}"/>
-    <hyperlink ref="G34" r:id="rId17" xr:uid="{00000000-0004-0000-0400-000010000000}"/>
-    <hyperlink ref="G35" r:id="rId18" xr:uid="{00000000-0004-0000-0400-000011000000}"/>
-    <hyperlink ref="G36" r:id="rId19" xr:uid="{00000000-0004-0000-0400-000012000000}"/>
-    <hyperlink ref="G37" r:id="rId20" xr:uid="{00000000-0004-0000-0400-000013000000}"/>
-    <hyperlink ref="G38" r:id="rId21" xr:uid="{00000000-0004-0000-0400-000014000000}"/>
-    <hyperlink ref="G39" r:id="rId22" xr:uid="{00000000-0004-0000-0400-000015000000}"/>
-  </hyperlinks>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:T60"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:S59"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
@@ -11187,37 +10948,34 @@
     <col min="5" max="5" width="45" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
     <col min="7" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="9" t="s">
-        <v>9</v>
-      </c>
+      <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -11228,36 +10986,33 @@
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-    </row>
-    <row r="2" spans="1:20" ht="43.2" customHeight="1">
-      <c r="A2" s="13" t="s">
-        <v>10</v>
+    </row>
+    <row r="2" spans="1:19" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>446</v>
+        <v>419</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>466</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>469</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>15</v>
-      </c>
       <c r="G2" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>26</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -11268,36 +11023,33 @@
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-    </row>
-    <row r="3" spans="1:20" ht="72" customHeight="1">
-      <c r="A3" s="13" t="s">
-        <v>18</v>
+    </row>
+    <row r="3" spans="1:19" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="12" t="s">
+        <v>14</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>15</v>
-      </c>
       <c r="G3" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>35</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -11308,36 +11060,33 @@
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
-      <c r="T3" s="1"/>
-    </row>
-    <row r="4" spans="1:20" ht="57.6" customHeight="1">
-      <c r="A4" s="13" t="s">
-        <v>24</v>
+    </row>
+    <row r="4" spans="1:19" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="12" t="s">
+        <v>19</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>447</v>
+        <v>420</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>467</v>
+        <v>439</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>470</v>
+        <v>442</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>23</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
@@ -11348,34 +11097,33 @@
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
-      <c r="T4" s="1"/>
-    </row>
-    <row r="5" spans="1:20" ht="57.6" customHeight="1">
-      <c r="A5" s="13" t="s">
-        <v>27</v>
+    </row>
+    <row r="5" spans="1:19" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="12" t="s">
+        <v>21</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>448</v>
+        <v>421</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>459</v>
+        <v>432</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>468</v>
+        <v>440</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>471</v>
+        <v>443</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="I5" s="7"/>
+        <v>13</v>
+      </c>
+      <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
@@ -11386,36 +11134,33 @@
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
-      <c r="T5" s="1"/>
-    </row>
-    <row r="6" spans="1:20" ht="57.6" customHeight="1">
-      <c r="A6" s="13" t="s">
-        <v>32</v>
+    </row>
+    <row r="6" spans="1:19" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
@@ -11426,36 +11171,17 @@
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
-      <c r="T6" s="1"/>
-    </row>
-    <row r="7" spans="1:20" ht="43.2">
-      <c r="A7" s="13" t="s">
-        <v>463</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>17</v>
-      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
@@ -11466,9 +11192,8 @@
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
-      <c r="T7" s="1"/>
-    </row>
-    <row r="8" spans="1:20">
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -11488,9 +11213,8 @@
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
-      <c r="T8" s="1"/>
-    </row>
-    <row r="9" spans="1:20">
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -11510,9 +11234,8 @@
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
-      <c r="T9" s="1"/>
-    </row>
-    <row r="10" spans="1:20">
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -11532,9 +11255,8 @@
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
-      <c r="T10" s="1"/>
-    </row>
-    <row r="11" spans="1:20">
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -11554,9 +11276,8 @@
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
-      <c r="T11" s="1"/>
-    </row>
-    <row r="12" spans="1:20">
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -11576,9 +11297,8 @@
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
-      <c r="T12" s="1"/>
-    </row>
-    <row r="13" spans="1:20">
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -11598,9 +11318,8 @@
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
-      <c r="T13" s="1"/>
-    </row>
-    <row r="14" spans="1:20">
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -11620,9 +11339,8 @@
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
-      <c r="T14" s="1"/>
-    </row>
-    <row r="15" spans="1:20">
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -11642,9 +11360,8 @@
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
-      <c r="T15" s="1"/>
-    </row>
-    <row r="16" spans="1:20">
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -11664,9 +11381,8 @@
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
-      <c r="T16" s="1"/>
-    </row>
-    <row r="17" spans="1:20">
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -11686,9 +11402,8 @@
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
-      <c r="T17" s="1"/>
-    </row>
-    <row r="18" spans="1:20">
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -11708,9 +11423,8 @@
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
-      <c r="T18" s="1"/>
-    </row>
-    <row r="19" spans="1:20">
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -11730,9 +11444,8 @@
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
-      <c r="T19" s="1"/>
-    </row>
-    <row r="20" spans="1:20">
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -11752,9 +11465,8 @@
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
-      <c r="T20" s="1"/>
-    </row>
-    <row r="21" spans="1:20">
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -11774,9 +11486,8 @@
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
-      <c r="T21" s="1"/>
-    </row>
-    <row r="22" spans="1:20">
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -11796,9 +11507,8 @@
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
-      <c r="T22" s="1"/>
-    </row>
-    <row r="23" spans="1:20">
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -11818,9 +11528,8 @@
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
-      <c r="T23" s="1"/>
-    </row>
-    <row r="24" spans="1:20">
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -11840,9 +11549,8 @@
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
-      <c r="T24" s="1"/>
-    </row>
-    <row r="25" spans="1:20">
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -11862,9 +11570,8 @@
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
-      <c r="T25" s="1"/>
-    </row>
-    <row r="26" spans="1:20">
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -11884,9 +11591,8 @@
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
-      <c r="T26" s="1"/>
-    </row>
-    <row r="27" spans="1:20">
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -11906,9 +11612,8 @@
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
-      <c r="T27" s="1"/>
-    </row>
-    <row r="28" spans="1:20">
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -11928,9 +11633,8 @@
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
-      <c r="T28" s="1"/>
-    </row>
-    <row r="29" spans="1:20">
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -11950,9 +11654,8 @@
       <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
-      <c r="T29" s="1"/>
-    </row>
-    <row r="30" spans="1:20">
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -11972,9 +11675,8 @@
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
-      <c r="T30" s="1"/>
-    </row>
-    <row r="31" spans="1:20">
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -11994,9 +11696,8 @@
       <c r="Q31" s="1"/>
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
-      <c r="T31" s="1"/>
-    </row>
-    <row r="32" spans="1:20">
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -12016,9 +11717,8 @@
       <c r="Q32" s="1"/>
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
-      <c r="T32" s="1"/>
-    </row>
-    <row r="33" spans="1:20">
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -12038,9 +11738,8 @@
       <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
-      <c r="T33" s="1"/>
-    </row>
-    <row r="34" spans="1:20">
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -12060,9 +11759,8 @@
       <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
-      <c r="T34" s="1"/>
-    </row>
-    <row r="35" spans="1:20">
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -12082,9 +11780,8 @@
       <c r="Q35" s="1"/>
       <c r="R35" s="1"/>
       <c r="S35" s="1"/>
-      <c r="T35" s="1"/>
-    </row>
-    <row r="36" spans="1:20">
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -12104,9 +11801,8 @@
       <c r="Q36" s="1"/>
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
-      <c r="T36" s="1"/>
-    </row>
-    <row r="37" spans="1:20">
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -12126,9 +11822,8 @@
       <c r="Q37" s="1"/>
       <c r="R37" s="1"/>
       <c r="S37" s="1"/>
-      <c r="T37" s="1"/>
-    </row>
-    <row r="38" spans="1:20">
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -12148,9 +11843,8 @@
       <c r="Q38" s="1"/>
       <c r="R38" s="1"/>
       <c r="S38" s="1"/>
-      <c r="T38" s="1"/>
-    </row>
-    <row r="39" spans="1:20">
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -12170,9 +11864,8 @@
       <c r="Q39" s="1"/>
       <c r="R39" s="1"/>
       <c r="S39" s="1"/>
-      <c r="T39" s="1"/>
-    </row>
-    <row r="40" spans="1:20">
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -12192,9 +11885,8 @@
       <c r="Q40" s="1"/>
       <c r="R40" s="1"/>
       <c r="S40" s="1"/>
-      <c r="T40" s="1"/>
-    </row>
-    <row r="41" spans="1:20">
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -12214,9 +11906,8 @@
       <c r="Q41" s="1"/>
       <c r="R41" s="1"/>
       <c r="S41" s="1"/>
-      <c r="T41" s="1"/>
-    </row>
-    <row r="42" spans="1:20">
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -12236,9 +11927,8 @@
       <c r="Q42" s="1"/>
       <c r="R42" s="1"/>
       <c r="S42" s="1"/>
-      <c r="T42" s="1"/>
-    </row>
-    <row r="43" spans="1:20">
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -12258,9 +11948,8 @@
       <c r="Q43" s="1"/>
       <c r="R43" s="1"/>
       <c r="S43" s="1"/>
-      <c r="T43" s="1"/>
-    </row>
-    <row r="44" spans="1:20">
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -12280,9 +11969,8 @@
       <c r="Q44" s="1"/>
       <c r="R44" s="1"/>
       <c r="S44" s="1"/>
-      <c r="T44" s="1"/>
-    </row>
-    <row r="45" spans="1:20">
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -12302,9 +11990,8 @@
       <c r="Q45" s="1"/>
       <c r="R45" s="1"/>
       <c r="S45" s="1"/>
-      <c r="T45" s="1"/>
-    </row>
-    <row r="46" spans="1:20">
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -12324,9 +12011,8 @@
       <c r="Q46" s="1"/>
       <c r="R46" s="1"/>
       <c r="S46" s="1"/>
-      <c r="T46" s="1"/>
-    </row>
-    <row r="47" spans="1:20">
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -12346,9 +12032,8 @@
       <c r="Q47" s="1"/>
       <c r="R47" s="1"/>
       <c r="S47" s="1"/>
-      <c r="T47" s="1"/>
-    </row>
-    <row r="48" spans="1:20">
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -12368,9 +12053,8 @@
       <c r="Q48" s="1"/>
       <c r="R48" s="1"/>
       <c r="S48" s="1"/>
-      <c r="T48" s="1"/>
-    </row>
-    <row r="49" spans="1:20">
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -12390,9 +12074,8 @@
       <c r="Q49" s="1"/>
       <c r="R49" s="1"/>
       <c r="S49" s="1"/>
-      <c r="T49" s="1"/>
-    </row>
-    <row r="50" spans="1:20">
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -12412,9 +12095,8 @@
       <c r="Q50" s="1"/>
       <c r="R50" s="1"/>
       <c r="S50" s="1"/>
-      <c r="T50" s="1"/>
-    </row>
-    <row r="51" spans="1:20">
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -12434,9 +12116,8 @@
       <c r="Q51" s="1"/>
       <c r="R51" s="1"/>
       <c r="S51" s="1"/>
-      <c r="T51" s="1"/>
-    </row>
-    <row r="52" spans="1:20">
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -12456,9 +12137,8 @@
       <c r="Q52" s="1"/>
       <c r="R52" s="1"/>
       <c r="S52" s="1"/>
-      <c r="T52" s="1"/>
-    </row>
-    <row r="53" spans="1:20">
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -12478,9 +12158,8 @@
       <c r="Q53" s="1"/>
       <c r="R53" s="1"/>
       <c r="S53" s="1"/>
-      <c r="T53" s="1"/>
-    </row>
-    <row r="54" spans="1:20">
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -12500,9 +12179,8 @@
       <c r="Q54" s="1"/>
       <c r="R54" s="1"/>
       <c r="S54" s="1"/>
-      <c r="T54" s="1"/>
-    </row>
-    <row r="55" spans="1:20">
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -12522,9 +12200,8 @@
       <c r="Q55" s="1"/>
       <c r="R55" s="1"/>
       <c r="S55" s="1"/>
-      <c r="T55" s="1"/>
-    </row>
-    <row r="56" spans="1:20">
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -12544,9 +12221,8 @@
       <c r="Q56" s="1"/>
       <c r="R56" s="1"/>
       <c r="S56" s="1"/>
-      <c r="T56" s="1"/>
-    </row>
-    <row r="57" spans="1:20">
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -12566,9 +12242,8 @@
       <c r="Q57" s="1"/>
       <c r="R57" s="1"/>
       <c r="S57" s="1"/>
-      <c r="T57" s="1"/>
-    </row>
-    <row r="58" spans="1:20">
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -12588,9 +12263,8 @@
       <c r="Q58" s="1"/>
       <c r="R58" s="1"/>
       <c r="S58" s="1"/>
-      <c r="T58" s="1"/>
-    </row>
-    <row r="59" spans="1:20">
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -12610,42 +12284,9 @@
       <c r="Q59" s="1"/>
       <c r="R59" s="1"/>
       <c r="S59" s="1"/>
-      <c r="T59" s="1"/>
-    </row>
-    <row r="60" spans="1:20">
-      <c r="A60" s="1"/>
-      <c r="B60" s="1"/>
-      <c r="C60" s="1"/>
-      <c r="D60" s="1"/>
-      <c r="E60" s="1"/>
-      <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
-      <c r="H60" s="1"/>
-      <c r="I60" s="1"/>
-      <c r="J60" s="1"/>
-      <c r="K60" s="1"/>
-      <c r="L60" s="1"/>
-      <c r="M60" s="1"/>
-      <c r="N60" s="1"/>
-      <c r="O60" s="1"/>
-      <c r="P60" s="1"/>
-      <c r="Q60" s="1"/>
-      <c r="R60" s="1"/>
-      <c r="S60" s="1"/>
-      <c r="T60" s="1"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I7">
-    <sortCondition ref="A7"/>
-  </sortState>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="I7" r:id="rId1" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
-    <hyperlink ref="I4" r:id="rId2" xr:uid="{00000000-0004-0000-0500-000001000000}"/>
-    <hyperlink ref="I2" r:id="rId3" xr:uid="{00000000-0004-0000-0500-000002000000}"/>
-    <hyperlink ref="I6" r:id="rId4" xr:uid="{00000000-0004-0000-0500-000003000000}"/>
-    <hyperlink ref="I3" r:id="rId5" xr:uid="{00000000-0004-0000-0500-000005000000}"/>
-  </hyperlinks>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12653,25 +12294,25 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:V60"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="45" customWidth="1"/>
     <col min="3" max="4" width="65" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
-      <c r="A1" s="9" t="s">
-        <v>321</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>334</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>335</v>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>318</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -12692,18 +12333,18 @@
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
     </row>
-    <row r="2" spans="1:22" ht="28.8" customHeight="1">
+    <row r="2" spans="1:22" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>336</v>
+        <v>319</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>337</v>
+        <v>320</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
@@ -12724,18 +12365,18 @@
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
     </row>
-    <row r="3" spans="1:22" ht="28.8" customHeight="1">
+    <row r="3" spans="1:22" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>340</v>
+        <v>323</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>342</v>
+        <v>325</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -12756,18 +12397,18 @@
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
     </row>
-    <row r="4" spans="1:22" ht="28.8" customHeight="1">
+    <row r="4" spans="1:22" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>340</v>
+        <v>323</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>345</v>
+        <v>328</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
@@ -12788,18 +12429,18 @@
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
     </row>
-    <row r="5" spans="1:22" ht="28.8" customHeight="1">
+    <row r="5" spans="1:22" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>347</v>
+        <v>330</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>349</v>
+        <v>332</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>350</v>
+        <v>333</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -12820,18 +12461,18 @@
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
     </row>
-    <row r="6" spans="1:22" ht="28.8" customHeight="1">
+    <row r="6" spans="1:22" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>347</v>
+        <v>330</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>351</v>
+        <v>334</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>352</v>
+        <v>335</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>353</v>
+        <v>336</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
@@ -12852,18 +12493,18 @@
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
     </row>
-    <row r="7" spans="1:22" ht="28.8" customHeight="1">
+    <row r="7" spans="1:22" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>354</v>
+        <v>337</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>357</v>
+        <v>340</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
@@ -12884,18 +12525,18 @@
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
     </row>
-    <row r="8" spans="1:22" ht="28.8" customHeight="1">
+    <row r="8" spans="1:22" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>354</v>
+        <v>337</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>359</v>
+        <v>342</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>360</v>
+        <v>343</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
@@ -12916,7 +12557,7 @@
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -12940,7 +12581,7 @@
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -12964,7 +12605,7 @@
       <c r="U10" s="1"/>
       <c r="V10" s="1"/>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -12988,7 +12629,7 @@
       <c r="U11" s="1"/>
       <c r="V11" s="1"/>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -13012,7 +12653,7 @@
       <c r="U12" s="1"/>
       <c r="V12" s="1"/>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -13036,7 +12677,7 @@
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -13060,7 +12701,7 @@
       <c r="U14" s="1"/>
       <c r="V14" s="1"/>
     </row>
-    <row r="15" spans="1:22">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -13084,7 +12725,7 @@
       <c r="U15" s="1"/>
       <c r="V15" s="1"/>
     </row>
-    <row r="16" spans="1:22">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -13108,7 +12749,7 @@
       <c r="U16" s="1"/>
       <c r="V16" s="1"/>
     </row>
-    <row r="17" spans="1:22">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -13132,7 +12773,7 @@
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
     </row>
-    <row r="18" spans="1:22">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -13156,7 +12797,7 @@
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
     </row>
-    <row r="19" spans="1:22">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -13180,7 +12821,7 @@
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
     </row>
-    <row r="20" spans="1:22">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -13204,7 +12845,7 @@
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
     </row>
-    <row r="21" spans="1:22">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -13228,7 +12869,7 @@
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
     </row>
-    <row r="22" spans="1:22">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -13252,7 +12893,7 @@
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
     </row>
-    <row r="23" spans="1:22">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -13276,7 +12917,7 @@
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
     </row>
-    <row r="24" spans="1:22">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -13300,7 +12941,7 @@
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
     </row>
-    <row r="25" spans="1:22">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -13324,7 +12965,7 @@
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
     </row>
-    <row r="26" spans="1:22">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -13348,7 +12989,7 @@
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
     </row>
-    <row r="27" spans="1:22">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -13372,7 +13013,7 @@
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
     </row>
-    <row r="28" spans="1:22">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -13396,7 +13037,7 @@
       <c r="U28" s="1"/>
       <c r="V28" s="1"/>
     </row>
-    <row r="29" spans="1:22">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -13420,7 +13061,7 @@
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
     </row>
-    <row r="30" spans="1:22">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -13444,7 +13085,7 @@
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
     </row>
-    <row r="31" spans="1:22">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -13468,7 +13109,7 @@
       <c r="U31" s="1"/>
       <c r="V31" s="1"/>
     </row>
-    <row r="32" spans="1:22">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -13492,7 +13133,7 @@
       <c r="U32" s="1"/>
       <c r="V32" s="1"/>
     </row>
-    <row r="33" spans="1:22">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -13516,7 +13157,7 @@
       <c r="U33" s="1"/>
       <c r="V33" s="1"/>
     </row>
-    <row r="34" spans="1:22">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -13540,7 +13181,7 @@
       <c r="U34" s="1"/>
       <c r="V34" s="1"/>
     </row>
-    <row r="35" spans="1:22">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -13564,7 +13205,7 @@
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
     </row>
-    <row r="36" spans="1:22">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -13588,7 +13229,7 @@
       <c r="U36" s="1"/>
       <c r="V36" s="1"/>
     </row>
-    <row r="37" spans="1:22">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -13612,7 +13253,7 @@
       <c r="U37" s="1"/>
       <c r="V37" s="1"/>
     </row>
-    <row r="38" spans="1:22">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -13636,7 +13277,7 @@
       <c r="U38" s="1"/>
       <c r="V38" s="1"/>
     </row>
-    <row r="39" spans="1:22">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -13660,7 +13301,7 @@
       <c r="U39" s="1"/>
       <c r="V39" s="1"/>
     </row>
-    <row r="40" spans="1:22">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -13684,7 +13325,7 @@
       <c r="U40" s="1"/>
       <c r="V40" s="1"/>
     </row>
-    <row r="41" spans="1:22">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -13708,7 +13349,7 @@
       <c r="U41" s="1"/>
       <c r="V41" s="1"/>
     </row>
-    <row r="42" spans="1:22">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -13732,7 +13373,7 @@
       <c r="U42" s="1"/>
       <c r="V42" s="1"/>
     </row>
-    <row r="43" spans="1:22">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -13756,7 +13397,7 @@
       <c r="U43" s="1"/>
       <c r="V43" s="1"/>
     </row>
-    <row r="44" spans="1:22">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -13780,7 +13421,7 @@
       <c r="U44" s="1"/>
       <c r="V44" s="1"/>
     </row>
-    <row r="45" spans="1:22">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -13804,7 +13445,7 @@
       <c r="U45" s="1"/>
       <c r="V45" s="1"/>
     </row>
-    <row r="46" spans="1:22">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -13828,7 +13469,7 @@
       <c r="U46" s="1"/>
       <c r="V46" s="1"/>
     </row>
-    <row r="47" spans="1:22">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -13852,7 +13493,7 @@
       <c r="U47" s="1"/>
       <c r="V47" s="1"/>
     </row>
-    <row r="48" spans="1:22">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -13876,7 +13517,7 @@
       <c r="U48" s="1"/>
       <c r="V48" s="1"/>
     </row>
-    <row r="49" spans="1:22">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -13900,7 +13541,7 @@
       <c r="U49" s="1"/>
       <c r="V49" s="1"/>
     </row>
-    <row r="50" spans="1:22">
+    <row r="50" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -13924,7 +13565,7 @@
       <c r="U50" s="1"/>
       <c r="V50" s="1"/>
     </row>
-    <row r="51" spans="1:22">
+    <row r="51" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -13948,7 +13589,7 @@
       <c r="U51" s="1"/>
       <c r="V51" s="1"/>
     </row>
-    <row r="52" spans="1:22">
+    <row r="52" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -13972,7 +13613,7 @@
       <c r="U52" s="1"/>
       <c r="V52" s="1"/>
     </row>
-    <row r="53" spans="1:22">
+    <row r="53" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -13996,7 +13637,7 @@
       <c r="U53" s="1"/>
       <c r="V53" s="1"/>
     </row>
-    <row r="54" spans="1:22">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -14020,7 +13661,7 @@
       <c r="U54" s="1"/>
       <c r="V54" s="1"/>
     </row>
-    <row r="55" spans="1:22">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -14044,7 +13685,7 @@
       <c r="U55" s="1"/>
       <c r="V55" s="1"/>
     </row>
-    <row r="56" spans="1:22">
+    <row r="56" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -14068,7 +13709,7 @@
       <c r="U56" s="1"/>
       <c r="V56" s="1"/>
     </row>
-    <row r="57" spans="1:22">
+    <row r="57" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -14092,7 +13733,7 @@
       <c r="U57" s="1"/>
       <c r="V57" s="1"/>
     </row>
-    <row r="58" spans="1:22">
+    <row r="58" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -14116,7 +13757,7 @@
       <c r="U58" s="1"/>
       <c r="V58" s="1"/>
     </row>
-    <row r="59" spans="1:22">
+    <row r="59" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -14140,7 +13781,7 @@
       <c r="U59" s="1"/>
       <c r="V59" s="1"/>
     </row>
-    <row r="60" spans="1:22">
+    <row r="60" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -14172,17 +13813,17 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:V58"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
-      <c r="A1" s="27" t="s">
-        <v>361</v>
-      </c>
-      <c r="B1" s="25"/>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A1" s="22" t="s">
+        <v>344</v>
+      </c>
+      <c r="B1" s="20"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -14204,7 +13845,7 @@
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -14228,12 +13869,12 @@
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
     </row>
-    <row r="3" spans="1:22">
-      <c r="A3" s="11" t="s">
-        <v>362</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>426</v>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>409</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -14256,12 +13897,12 @@
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
     </row>
-    <row r="4" spans="1:22">
-      <c r="A4" s="18" t="s">
-        <v>363</v>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A4" s="17" t="s">
+        <v>346</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>364</v>
+        <v>347</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -14284,12 +13925,12 @@
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
     </row>
-    <row r="5" spans="1:22" ht="28.8" customHeight="1">
-      <c r="A5" s="18" t="s">
-        <v>365</v>
+    <row r="5" spans="1:22" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="17" t="s">
+        <v>348</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>366</v>
+        <v>349</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -14312,7 +13953,7 @@
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -14336,11 +13977,11 @@
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
     </row>
-    <row r="7" spans="1:22">
-      <c r="A7" s="26" t="s">
-        <v>367</v>
-      </c>
-      <c r="B7" s="25"/>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A7" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="B7" s="20"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -14362,9 +14003,9 @@
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
     </row>
-    <row r="8" spans="1:22">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>368</v>
+        <v>351</v>
       </c>
       <c r="B8" s="4">
         <f>'Test Execution Sheet'!B7</f>
@@ -14391,9 +14032,9 @@
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>369</v>
+        <v>352</v>
       </c>
       <c r="B9" s="4">
         <f>'Test Execution Sheet'!B7</f>
@@ -14420,9 +14061,9 @@
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>370</v>
+        <v>353</v>
       </c>
       <c r="B10" s="4">
         <f>'Test Execution Sheet'!B8</f>
@@ -14449,9 +14090,9 @@
       <c r="U10" s="1"/>
       <c r="V10" s="1"/>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>371</v>
+        <v>354</v>
       </c>
       <c r="B11" s="4">
         <f>'Test Execution Sheet'!B9</f>
@@ -14478,9 +14119,9 @@
       <c r="U11" s="1"/>
       <c r="V11" s="1"/>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="B12" s="4">
         <f>'Test Execution Sheet'!B10</f>
@@ -14507,9 +14148,9 @@
       <c r="U12" s="1"/>
       <c r="V12" s="1"/>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="B13" s="4">
         <f>B10/B9</f>
@@ -14536,7 +14177,7 @@
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -14560,11 +14201,11 @@
       <c r="U14" s="1"/>
       <c r="V14" s="1"/>
     </row>
-    <row r="15" spans="1:22">
-      <c r="A15" s="26" t="s">
-        <v>372</v>
-      </c>
-      <c r="B15" s="25"/>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A15" s="21" t="s">
+        <v>355</v>
+      </c>
+      <c r="B15" s="20"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
@@ -14586,12 +14227,12 @@
       <c r="U15" s="1"/>
       <c r="V15" s="1"/>
     </row>
-    <row r="16" spans="1:22">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>373</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>472</v>
+        <v>356</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>444</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -14614,12 +14255,12 @@
       <c r="U16" s="1"/>
       <c r="V16" s="1"/>
     </row>
-    <row r="17" spans="1:22">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="B17" s="15" t="s">
-        <v>473</v>
+        <v>357</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>445</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -14642,12 +14283,12 @@
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
     </row>
-    <row r="18" spans="1:22">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="B18" s="15" t="s">
-        <v>376</v>
+        <v>358</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>359</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
@@ -14670,7 +14311,7 @@
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
     </row>
-    <row r="19" spans="1:22">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -14694,11 +14335,11 @@
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
     </row>
-    <row r="20" spans="1:22">
-      <c r="A20" s="26" t="s">
-        <v>377</v>
-      </c>
-      <c r="B20" s="25"/>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A20" s="21" t="s">
+        <v>360</v>
+      </c>
+      <c r="B20" s="20"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
@@ -14720,12 +14361,12 @@
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
     </row>
-    <row r="21" spans="1:22" ht="28.8">
+    <row r="21" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>378</v>
-      </c>
-      <c r="B21" s="17" t="s">
-        <v>431</v>
+        <v>361</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>414</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -14748,7 +14389,7 @@
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
     </row>
-    <row r="22" spans="1:22">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -14772,11 +14413,11 @@
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
     </row>
-    <row r="23" spans="1:22">
-      <c r="A23" s="26" t="s">
-        <v>379</v>
-      </c>
-      <c r="B23" s="25"/>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A23" s="21" t="s">
+        <v>362</v>
+      </c>
+      <c r="B23" s="20"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -14798,9 +14439,9 @@
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
     </row>
-    <row r="24" spans="1:22">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>380</v>
+        <v>363</v>
       </c>
       <c r="B24" s="4">
         <v>5</v>
@@ -14826,12 +14467,12 @@
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
     </row>
-    <row r="25" spans="1:22">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="B25" s="4">
-        <f>COUNTIF('Defect Tracking Sheet'!F2:F10, "Critical")</f>
+        <f>COUNTIF('Defect Tracking Sheet'!F2:F9, "Critical")</f>
         <v>0</v>
       </c>
       <c r="C25" s="1"/>
@@ -14855,12 +14496,12 @@
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
     </row>
-    <row r="26" spans="1:22">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>382</v>
+        <v>365</v>
       </c>
       <c r="B26" s="4">
-        <f>COUNTIF('Defect Tracking Sheet'!F2:F10, "High")</f>
+        <f>COUNTIF('Defect Tracking Sheet'!F2:F9, "High")</f>
         <v>3</v>
       </c>
       <c r="C26" s="1"/>
@@ -14884,13 +14525,13 @@
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
     </row>
-    <row r="27" spans="1:22">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>383</v>
+        <v>366</v>
       </c>
       <c r="B27" s="4">
-        <f>COUNTIF('Defect Tracking Sheet'!F2:F10, "Medium")</f>
-        <v>3</v>
+        <f>COUNTIF('Defect Tracking Sheet'!F2:F9, "Medium")</f>
+        <v>2</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
@@ -14913,12 +14554,12 @@
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
     </row>
-    <row r="28" spans="1:22">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>384</v>
+        <v>367</v>
       </c>
       <c r="B28" s="4">
-        <f>COUNTIF('Defect Tracking Sheet'!F2:F10, "Low")</f>
+        <f>COUNTIF('Defect Tracking Sheet'!F2:F9, "Low")</f>
         <v>0</v>
       </c>
       <c r="C28" s="1"/>
@@ -14942,7 +14583,7 @@
       <c r="U28" s="1"/>
       <c r="V28" s="1"/>
     </row>
-    <row r="29" spans="1:22">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -14966,11 +14607,11 @@
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
     </row>
-    <row r="30" spans="1:22">
-      <c r="A30" s="26" t="s">
-        <v>385</v>
-      </c>
-      <c r="B30" s="25"/>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A30" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="B30" s="20"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
@@ -14992,12 +14633,12 @@
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
     </row>
-    <row r="31" spans="1:22">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>387</v>
+        <v>370</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -15020,12 +14661,12 @@
       <c r="U31" s="1"/>
       <c r="V31" s="1"/>
     </row>
-    <row r="32" spans="1:22">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="B32" s="15" t="s">
-        <v>430</v>
+        <v>371</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>413</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
@@ -15048,12 +14689,12 @@
       <c r="U32" s="1"/>
       <c r="V32" s="1"/>
     </row>
-    <row r="33" spans="1:22">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>389</v>
+        <v>372</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>390</v>
+        <v>373</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
@@ -15076,12 +14717,12 @@
       <c r="U33" s="1"/>
       <c r="V33" s="1"/>
     </row>
-    <row r="34" spans="1:22">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>391</v>
-      </c>
-      <c r="B34" s="15" t="s">
-        <v>432</v>
+        <v>374</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>415</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
@@ -15104,12 +14745,12 @@
       <c r="U34" s="1"/>
       <c r="V34" s="1"/>
     </row>
-    <row r="35" spans="1:22">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>392</v>
-      </c>
-      <c r="B35" s="17" t="s">
-        <v>433</v>
+        <v>375</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>416</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
@@ -15132,12 +14773,12 @@
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
     </row>
-    <row r="36" spans="1:22">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>393</v>
-      </c>
-      <c r="B36" s="17" t="s">
-        <v>394</v>
+        <v>376</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>377</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
@@ -15155,7 +14796,7 @@
       <c r="U36" s="1"/>
       <c r="V36" s="1"/>
     </row>
-    <row r="37" spans="1:22">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -15173,11 +14814,11 @@
       <c r="U37" s="1"/>
       <c r="V37" s="1"/>
     </row>
-    <row r="38" spans="1:22">
-      <c r="A38" s="26" t="s">
-        <v>395</v>
-      </c>
-      <c r="B38" s="25"/>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A38" s="21" t="s">
+        <v>378</v>
+      </c>
+      <c r="B38" s="20"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
@@ -15193,12 +14834,12 @@
       <c r="U38" s="1"/>
       <c r="V38" s="1"/>
     </row>
-    <row r="39" spans="1:22">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>396</v>
-      </c>
-      <c r="B39" s="17" t="s">
-        <v>397</v>
+        <v>379</v>
+      </c>
+      <c r="B39" s="16" t="s">
+        <v>380</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
@@ -15215,12 +14856,12 @@
       <c r="U39" s="1"/>
       <c r="V39" s="1"/>
     </row>
-    <row r="40" spans="1:22">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>398</v>
+        <v>381</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>399</v>
+        <v>382</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
@@ -15238,7 +14879,7 @@
       <c r="U40" s="1"/>
       <c r="V40" s="1"/>
     </row>
-    <row r="41" spans="1:22">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -15257,11 +14898,11 @@
       <c r="U41" s="1"/>
       <c r="V41" s="1"/>
     </row>
-    <row r="42" spans="1:22">
-      <c r="A42" s="26" t="s">
-        <v>400</v>
-      </c>
-      <c r="B42" s="25"/>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A42" s="21" t="s">
+        <v>383</v>
+      </c>
+      <c r="B42" s="20"/>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
@@ -15278,11 +14919,11 @@
       <c r="U42" s="1"/>
       <c r="V42" s="1"/>
     </row>
-    <row r="43" spans="1:22">
-      <c r="A43" s="24" t="s">
-        <v>434</v>
-      </c>
-      <c r="B43" s="25"/>
+    <row r="43" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A43" s="19" t="s">
+        <v>417</v>
+      </c>
+      <c r="B43" s="20"/>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
@@ -15304,7 +14945,7 @@
       <c r="U43" s="1"/>
       <c r="V43" s="1"/>
     </row>
-    <row r="44" spans="1:22">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -15328,7 +14969,7 @@
       <c r="U44" s="1"/>
       <c r="V44" s="1"/>
     </row>
-    <row r="45" spans="1:22">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -15350,7 +14991,7 @@
       <c r="U45" s="1"/>
       <c r="V45" s="1"/>
     </row>
-    <row r="46" spans="1:22">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -15372,7 +15013,7 @@
       <c r="U46" s="1"/>
       <c r="V46" s="1"/>
     </row>
-    <row r="47" spans="1:22">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -15394,7 +15035,7 @@
       <c r="U47" s="1"/>
       <c r="V47" s="1"/>
     </row>
-    <row r="48" spans="1:22">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -15418,7 +15059,7 @@
       <c r="U48" s="1"/>
       <c r="V48" s="1"/>
     </row>
-    <row r="49" spans="1:22">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -15442,7 +15083,7 @@
       <c r="U49" s="1"/>
       <c r="V49" s="1"/>
     </row>
-    <row r="50" spans="1:22">
+    <row r="50" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -15466,7 +15107,7 @@
       <c r="U50" s="1"/>
       <c r="V50" s="1"/>
     </row>
-    <row r="51" spans="1:22">
+    <row r="51" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -15490,7 +15131,7 @@
       <c r="U51" s="1"/>
       <c r="V51" s="1"/>
     </row>
-    <row r="52" spans="1:22">
+    <row r="52" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -15514,7 +15155,7 @@
       <c r="U52" s="1"/>
       <c r="V52" s="1"/>
     </row>
-    <row r="53" spans="1:22">
+    <row r="53" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -15538,7 +15179,7 @@
       <c r="U53" s="1"/>
       <c r="V53" s="1"/>
     </row>
-    <row r="54" spans="1:22">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -15562,7 +15203,7 @@
       <c r="U54" s="1"/>
       <c r="V54" s="1"/>
     </row>
-    <row r="55" spans="1:22">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -15586,7 +15227,7 @@
       <c r="U55" s="1"/>
       <c r="V55" s="1"/>
     </row>
-    <row r="56" spans="1:22">
+    <row r="56" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -15610,7 +15251,7 @@
       <c r="U56" s="1"/>
       <c r="V56" s="1"/>
     </row>
-    <row r="57" spans="1:22">
+    <row r="57" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -15634,7 +15275,7 @@
       <c r="U57" s="1"/>
       <c r="V57" s="1"/>
     </row>
-    <row r="58" spans="1:22">
+    <row r="58" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
